--- a/research/traditional_assets/database/data/italy/italy_education.xlsx
+++ b/research/traditional_assets/database/data/italy/italy_education.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1004107639701648</v>
+        <v>0.1002039781366364</v>
       </c>
       <c r="C2">
-        <v>14.58320242530241</v>
+        <v>14.44786195696574</v>
       </c>
       <c r="D2">
-        <v>11.19320242530241</v>
+        <v>11.20370195696574</v>
       </c>
       <c r="E2">
-        <v>-0.6840000000000001</v>
+        <v>-0.5381600000000001</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.14584</v>
       </c>
       <c r="G2">
         <v>3.39</v>
@@ -1445,28 +1445,28 @@
         <v>1.29</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.007335751999999999</v>
       </c>
       <c r="N2">
-        <v>1.29</v>
+        <v>1.282664248</v>
       </c>
       <c r="O2">
-        <v>0.3095999999999999</v>
+        <v>0.30783941952</v>
       </c>
       <c r="P2">
-        <v>0.9803999999999999</v>
+        <v>0.9748248284799998</v>
       </c>
       <c r="Q2">
-        <v>2.7804</v>
+        <v>2.77482482848</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1004107639701648</v>
+        <v>0.1008299981178146</v>
       </c>
       <c r="T2">
-        <v>0.7517377218129921</v>
+        <v>0.7575086376572131</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>175.8510920216496</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1002039781366364</v>
+        <v>0.09999719230310802</v>
       </c>
       <c r="C3">
-        <v>14.44786195696574</v>
+        <v>14.31254120482224</v>
       </c>
       <c r="D3">
-        <v>11.20370195696574</v>
+        <v>11.21422120482224</v>
       </c>
       <c r="E3">
-        <v>-0.5381600000000001</v>
+        <v>-0.3923200000000001</v>
       </c>
       <c r="F3">
-        <v>0.14584</v>
+        <v>0.29168</v>
       </c>
       <c r="G3">
         <v>3.39</v>
@@ -1527,28 +1527,28 @@
         <v>1.29</v>
       </c>
       <c r="M3">
-        <v>0.007335751999999999</v>
+        <v>0.014671504</v>
       </c>
       <c r="N3">
-        <v>1.282664248</v>
+        <v>1.275328496</v>
       </c>
       <c r="O3">
-        <v>0.30783941952</v>
+        <v>0.3060788390399999</v>
       </c>
       <c r="P3">
-        <v>0.9748248284799998</v>
+        <v>0.9692496569599998</v>
       </c>
       <c r="Q3">
-        <v>2.77482482848</v>
+        <v>2.76924965696</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1008299981178146</v>
+        <v>0.1012577880643959</v>
       </c>
       <c r="T3">
-        <v>0.7575086376572131</v>
+        <v>0.7633973272941732</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>175.8510920216496</v>
+        <v>87.92554601082479</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09999719230310802</v>
+        <v>0.09979040646957964</v>
       </c>
       <c r="C4">
-        <v>14.31254120482224</v>
+        <v>14.17724022445917</v>
       </c>
       <c r="D4">
-        <v>11.21422120482224</v>
+        <v>11.22476022445917</v>
       </c>
       <c r="E4">
-        <v>-0.3923200000000001</v>
+        <v>-0.2464800000000001</v>
       </c>
       <c r="F4">
-        <v>0.29168</v>
+        <v>0.43752</v>
       </c>
       <c r="G4">
         <v>3.39</v>
@@ -1609,28 +1609,28 @@
         <v>1.29</v>
       </c>
       <c r="M4">
-        <v>0.014671504</v>
+        <v>0.022007256</v>
       </c>
       <c r="N4">
-        <v>1.275328496</v>
+        <v>1.267992744</v>
       </c>
       <c r="O4">
-        <v>0.3060788390399999</v>
+        <v>0.3043182585599999</v>
       </c>
       <c r="P4">
-        <v>0.9692496569599998</v>
+        <v>0.9636744854399999</v>
       </c>
       <c r="Q4">
-        <v>2.76924965696</v>
+        <v>2.76367448544</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1012577880643959</v>
+        <v>0.1016943984222471</v>
       </c>
       <c r="T4">
-        <v>0.7633973272941732</v>
+        <v>0.7694074332123079</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>87.92554601082479</v>
+        <v>58.6170306738832</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09979040646957964</v>
+        <v>0.09958362063605125</v>
       </c>
       <c r="C5">
-        <v>14.17724022445917</v>
+        <v>14.04195907167298</v>
       </c>
       <c r="D5">
-        <v>11.22476022445917</v>
+        <v>11.23531907167298</v>
       </c>
       <c r="E5">
-        <v>-0.2464800000000001</v>
+        <v>-0.1006400000000001</v>
       </c>
       <c r="F5">
-        <v>0.43752</v>
+        <v>0.58336</v>
       </c>
       <c r="G5">
         <v>3.39</v>
@@ -1691,28 +1691,28 @@
         <v>1.29</v>
       </c>
       <c r="M5">
-        <v>0.022007256</v>
+        <v>0.029343008</v>
       </c>
       <c r="N5">
-        <v>1.267992744</v>
+        <v>1.260656992</v>
       </c>
       <c r="O5">
-        <v>0.3043182585599999</v>
+        <v>0.3025576780799999</v>
       </c>
       <c r="P5">
-        <v>0.9636744854399999</v>
+        <v>0.95809931392</v>
       </c>
       <c r="Q5">
-        <v>2.76367448544</v>
+        <v>2.75809931392</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1016943984222471</v>
+        <v>0.1021401048292201</v>
       </c>
       <c r="T5">
-        <v>0.7694074332123079</v>
+        <v>0.7755427496704036</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>58.6170306738832</v>
+        <v>43.9627730054124</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09958362063605125</v>
+        <v>0.09937683480252284</v>
       </c>
       <c r="C6">
-        <v>14.04195907167298</v>
+        <v>13.90669780247024</v>
       </c>
       <c r="D6">
-        <v>11.23531907167298</v>
+        <v>11.24589780247024</v>
       </c>
       <c r="E6">
-        <v>-0.1006400000000001</v>
+        <v>0.04520000000000002</v>
       </c>
       <c r="F6">
-        <v>0.58336</v>
+        <v>0.7292000000000001</v>
       </c>
       <c r="G6">
         <v>3.39</v>
@@ -1773,28 +1773,28 @@
         <v>1.29</v>
       </c>
       <c r="M6">
-        <v>0.029343008</v>
+        <v>0.03667876</v>
       </c>
       <c r="N6">
-        <v>1.260656992</v>
+        <v>1.25332124</v>
       </c>
       <c r="O6">
-        <v>0.3025576780799999</v>
+        <v>0.3007970976</v>
       </c>
       <c r="P6">
-        <v>0.95809931392</v>
+        <v>0.9525241423999998</v>
       </c>
       <c r="Q6">
-        <v>2.75809931392</v>
+        <v>2.7525241424</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1021401048292201</v>
+        <v>0.1025951945289714</v>
       </c>
       <c r="T6">
-        <v>0.7755427496704036</v>
+        <v>0.7818072306855118</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>43.9627730054124</v>
+        <v>35.17021840432991</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09937683480252284</v>
+        <v>0.09917004896899446</v>
       </c>
       <c r="C7">
-        <v>13.90669780247024</v>
+        <v>13.77145647306867</v>
       </c>
       <c r="D7">
-        <v>11.24589780247024</v>
+        <v>11.25649647306867</v>
       </c>
       <c r="E7">
-        <v>0.04520000000000002</v>
+        <v>0.19104</v>
       </c>
       <c r="F7">
-        <v>0.7292000000000001</v>
+        <v>0.87504</v>
       </c>
       <c r="G7">
         <v>3.39</v>
@@ -1855,28 +1855,28 @@
         <v>1.29</v>
       </c>
       <c r="M7">
-        <v>0.03667876</v>
+        <v>0.044014512</v>
       </c>
       <c r="N7">
-        <v>1.25332124</v>
+        <v>1.245985488</v>
       </c>
       <c r="O7">
-        <v>0.3007970976</v>
+        <v>0.29903651712</v>
       </c>
       <c r="P7">
-        <v>0.9525241423999998</v>
+        <v>0.9469489708799999</v>
       </c>
       <c r="Q7">
-        <v>2.7525241424</v>
+        <v>2.74694897088</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1025951945289714</v>
+        <v>0.103059966988292</v>
       </c>
       <c r="T7">
-        <v>0.7818072306855118</v>
+        <v>0.7882049985307288</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>35.17021840432991</v>
+        <v>29.3085153369416</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09917004896899446</v>
+        <v>0.09896326313546606</v>
       </c>
       <c r="C8">
-        <v>13.77145647306867</v>
+        <v>13.63623513989811</v>
       </c>
       <c r="D8">
-        <v>11.25649647306867</v>
+        <v>11.26711513989811</v>
       </c>
       <c r="E8">
-        <v>0.1910399999999999</v>
+        <v>0.3368799999999997</v>
       </c>
       <c r="F8">
-        <v>0.8750399999999999</v>
+        <v>1.02088</v>
       </c>
       <c r="G8">
         <v>3.39</v>
@@ -1937,28 +1937,28 @@
         <v>1.29</v>
       </c>
       <c r="M8">
-        <v>0.04401451199999999</v>
+        <v>0.05135026399999999</v>
       </c>
       <c r="N8">
-        <v>1.245985488</v>
+        <v>1.238649736</v>
       </c>
       <c r="O8">
-        <v>0.29903651712</v>
+        <v>0.2972759366399999</v>
       </c>
       <c r="P8">
-        <v>0.9469489708799999</v>
+        <v>0.9413737993599998</v>
       </c>
       <c r="Q8">
-        <v>2.74694897088</v>
+        <v>2.74137379936</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.103059966988292</v>
+        <v>0.1035347345542646</v>
       </c>
       <c r="T8">
-        <v>0.7882049985307288</v>
+        <v>0.7947403527812191</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>29.3085153369416</v>
+        <v>25.12158457452137</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09896326313546605</v>
+        <v>0.09875647730193768</v>
       </c>
       <c r="C9">
-        <v>13.63623513989811</v>
+        <v>13.50103385960154</v>
       </c>
       <c r="D9">
-        <v>11.26711513989811</v>
+        <v>11.27775385960154</v>
       </c>
       <c r="E9">
-        <v>0.33688</v>
+        <v>0.4827199999999999</v>
       </c>
       <c r="F9">
-        <v>1.02088</v>
+        <v>1.16672</v>
       </c>
       <c r="G9">
         <v>3.39</v>
@@ -2019,28 +2019,28 @@
         <v>1.29</v>
       </c>
       <c r="M9">
-        <v>0.051350264</v>
+        <v>0.05868601599999999</v>
       </c>
       <c r="N9">
-        <v>1.238649736</v>
+        <v>1.231313984</v>
       </c>
       <c r="O9">
-        <v>0.2972759366399999</v>
+        <v>0.29551535616</v>
       </c>
       <c r="P9">
-        <v>0.9413737993599998</v>
+        <v>0.9357986278399999</v>
       </c>
       <c r="Q9">
-        <v>2.74137379936</v>
+        <v>2.73579862784</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1035347345542646</v>
+        <v>0.1040198231542801</v>
       </c>
       <c r="T9">
-        <v>0.7947403527812191</v>
+        <v>0.8014177799501985</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>25.12158457452136</v>
+        <v>21.9813865027062</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09875647730193768</v>
+        <v>0.09854969146840928</v>
       </c>
       <c r="C10">
-        <v>13.50103385960154</v>
+        <v>13.36585268903606</v>
       </c>
       <c r="D10">
-        <v>11.27775385960154</v>
+        <v>11.28841268903605</v>
       </c>
       <c r="E10">
-        <v>0.4827199999999999</v>
+        <v>0.6285599999999999</v>
       </c>
       <c r="F10">
-        <v>1.16672</v>
+        <v>1.31256</v>
       </c>
       <c r="G10">
         <v>3.39</v>
@@ -2101,28 +2101,28 @@
         <v>1.29</v>
       </c>
       <c r="M10">
-        <v>0.05868601599999999</v>
+        <v>0.06602176799999999</v>
       </c>
       <c r="N10">
-        <v>1.231313984</v>
+        <v>1.223978232</v>
       </c>
       <c r="O10">
-        <v>0.29551535616</v>
+        <v>0.29375477568</v>
       </c>
       <c r="P10">
-        <v>0.9357986278399999</v>
+        <v>0.9302234563199999</v>
       </c>
       <c r="Q10">
-        <v>2.73579862784</v>
+        <v>2.73022345632</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1040198231542801</v>
+        <v>0.104515573042208</v>
       </c>
       <c r="T10">
-        <v>0.8014177799501985</v>
+        <v>0.8082419637602544</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>21.9813865027062</v>
+        <v>19.53901022462773</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09854969146840928</v>
+        <v>0.09834290563488089</v>
       </c>
       <c r="C11">
-        <v>13.36585268903606</v>
+        <v>13.23069168527392</v>
       </c>
       <c r="D11">
-        <v>11.28841268903605</v>
+        <v>11.29909168527392</v>
       </c>
       <c r="E11">
-        <v>0.6285599999999999</v>
+        <v>0.7743999999999999</v>
       </c>
       <c r="F11">
-        <v>1.31256</v>
+        <v>1.4584</v>
       </c>
       <c r="G11">
         <v>3.39</v>
@@ -2183,28 +2183,28 @@
         <v>1.29</v>
       </c>
       <c r="M11">
-        <v>0.06602176799999999</v>
+        <v>0.07335752</v>
       </c>
       <c r="N11">
-        <v>1.223978232</v>
+        <v>1.21664248</v>
       </c>
       <c r="O11">
-        <v>0.29375477568</v>
+        <v>0.2919941951999999</v>
       </c>
       <c r="P11">
-        <v>0.9302234563199999</v>
+        <v>0.9246482847999998</v>
       </c>
       <c r="Q11">
-        <v>2.73022345632</v>
+        <v>2.7246482848</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.104515573042208</v>
+        <v>0.1050223395943121</v>
       </c>
       <c r="T11">
-        <v>0.8082419637602544</v>
+        <v>0.8152177960994227</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>19.53901022462773</v>
+        <v>17.58510920216496</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09834290563488089</v>
+        <v>0.09813611980135249</v>
       </c>
       <c r="C12">
-        <v>13.23069168527392</v>
+        <v>13.09555090560357</v>
       </c>
       <c r="D12">
-        <v>11.29909168527392</v>
+        <v>11.30979090560357</v>
       </c>
       <c r="E12">
-        <v>0.7744000000000001</v>
+        <v>0.9202399999999998</v>
       </c>
       <c r="F12">
-        <v>1.4584</v>
+        <v>1.60424</v>
       </c>
       <c r="G12">
         <v>3.39</v>
@@ -2265,28 +2265,28 @@
         <v>1.29</v>
       </c>
       <c r="M12">
-        <v>0.07335752000000001</v>
+        <v>0.080693272</v>
       </c>
       <c r="N12">
-        <v>1.21664248</v>
+        <v>1.209306728</v>
       </c>
       <c r="O12">
-        <v>0.2919941951999999</v>
+        <v>0.2902336147199999</v>
       </c>
       <c r="P12">
-        <v>0.9246482847999998</v>
+        <v>0.9190731132799999</v>
       </c>
       <c r="Q12">
-        <v>2.7246482848</v>
+        <v>2.71907311328</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1050223395943121</v>
+        <v>0.105540494158823</v>
       </c>
       <c r="T12">
-        <v>0.8152177960994227</v>
+        <v>0.8223503887158755</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>17.58510920216495</v>
+        <v>15.98646291105905</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09813611980135249</v>
+        <v>0.09792933396782408</v>
       </c>
       <c r="C13">
-        <v>13.09555090560357</v>
+        <v>12.96043040753063</v>
       </c>
       <c r="D13">
-        <v>11.30979090560357</v>
+        <v>11.32051040753063</v>
       </c>
       <c r="E13">
-        <v>0.9202399999999998</v>
+        <v>1.06608</v>
       </c>
       <c r="F13">
-        <v>1.60424</v>
+        <v>1.75008</v>
       </c>
       <c r="G13">
         <v>3.39</v>
@@ -2347,28 +2347,28 @@
         <v>1.29</v>
       </c>
       <c r="M13">
-        <v>0.080693272</v>
+        <v>0.08802902399999998</v>
       </c>
       <c r="N13">
-        <v>1.209306728</v>
+        <v>1.201970976</v>
       </c>
       <c r="O13">
-        <v>0.2902336147199999</v>
+        <v>0.28847303424</v>
       </c>
       <c r="P13">
-        <v>0.9190731132799999</v>
+        <v>0.91349794176</v>
       </c>
       <c r="Q13">
-        <v>2.71907311328</v>
+        <v>2.71349794176</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.105540494158823</v>
+        <v>0.1060704249634365</v>
       </c>
       <c r="T13">
-        <v>0.8223503887158755</v>
+        <v>0.8296450857099749</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>15.98646291105905</v>
+        <v>14.6542576684708</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09792933396782408</v>
+        <v>0.09772254813429569</v>
       </c>
       <c r="C14">
-        <v>12.96043040753063</v>
+        <v>12.82533024877894</v>
       </c>
       <c r="D14">
-        <v>11.32051040753063</v>
+        <v>11.33125024877894</v>
       </c>
       <c r="E14">
-        <v>1.06608</v>
+        <v>1.21192</v>
       </c>
       <c r="F14">
-        <v>1.75008</v>
+        <v>1.89592</v>
       </c>
       <c r="G14">
         <v>3.39</v>
@@ -2429,28 +2429,28 @@
         <v>1.29</v>
       </c>
       <c r="M14">
-        <v>0.08802902399999998</v>
+        <v>0.095364776</v>
       </c>
       <c r="N14">
-        <v>1.201970976</v>
+        <v>1.194635224</v>
       </c>
       <c r="O14">
-        <v>0.28847303424</v>
+        <v>0.2867124537599999</v>
       </c>
       <c r="P14">
-        <v>0.91349794176</v>
+        <v>0.9079227702399999</v>
       </c>
       <c r="Q14">
-        <v>2.71349794176</v>
+        <v>2.70792277024</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1060704249634365</v>
+        <v>0.1066125380853973</v>
       </c>
       <c r="T14">
-        <v>0.8296450857099749</v>
+        <v>0.8371074768878469</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>14.6542576684708</v>
+        <v>13.52700707858843</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09772254813429569</v>
+        <v>0.0976753623007673</v>
       </c>
       <c r="C15">
-        <v>12.82533024877894</v>
+        <v>12.68194379678721</v>
       </c>
       <c r="D15">
-        <v>11.33125024877894</v>
+        <v>11.33370379678721</v>
       </c>
       <c r="E15">
-        <v>1.21192</v>
+        <v>1.35776</v>
       </c>
       <c r="F15">
-        <v>1.89592</v>
+        <v>2.04176</v>
       </c>
       <c r="G15">
         <v>3.39</v>
@@ -2511,45 +2511,45 @@
         <v>1.29</v>
       </c>
       <c r="M15">
-        <v>0.095364776</v>
+        <v>0.105763168</v>
       </c>
       <c r="N15">
-        <v>1.194635224</v>
+        <v>1.184236832</v>
       </c>
       <c r="O15">
-        <v>0.2867124537599999</v>
+        <v>0.2842168396799999</v>
       </c>
       <c r="P15">
-        <v>0.9079227702399999</v>
+        <v>0.9000199923199999</v>
       </c>
       <c r="Q15">
-        <v>2.70792277024</v>
+        <v>2.70001999232</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1066125380853973</v>
+        <v>0.1071672584892643</v>
       </c>
       <c r="T15">
-        <v>0.8371074768878469</v>
+        <v>0.8447434120465995</v>
       </c>
       <c r="U15">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V15">
         <v>0.24</v>
       </c>
       <c r="W15">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y15">
-        <v>13.52700707858843</v>
+        <v>12.19706278087282</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.0976753623007673</v>
+        <v>0.0974799764672389</v>
       </c>
       <c r="C16">
-        <v>12.68194379678721</v>
+        <v>12.54627470162347</v>
       </c>
       <c r="D16">
-        <v>11.33370379678721</v>
+        <v>11.34387470162346</v>
       </c>
       <c r="E16">
-        <v>1.35776</v>
+        <v>1.5036</v>
       </c>
       <c r="F16">
-        <v>2.04176</v>
+        <v>2.1876</v>
       </c>
       <c r="G16">
         <v>3.39</v>
@@ -2593,28 +2593,28 @@
         <v>1.29</v>
       </c>
       <c r="M16">
-        <v>0.105763168</v>
+        <v>0.11331768</v>
       </c>
       <c r="N16">
-        <v>1.184236832</v>
+        <v>1.17668232</v>
       </c>
       <c r="O16">
-        <v>0.2842168396799999</v>
+        <v>0.2824037568</v>
       </c>
       <c r="P16">
-        <v>0.9000199923199999</v>
+        <v>0.8942785631999999</v>
       </c>
       <c r="Q16">
-        <v>2.70001999232</v>
+        <v>2.6942785632</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1071672584892643</v>
+        <v>0.1077350311379281</v>
       </c>
       <c r="T16">
-        <v>0.8447434120465995</v>
+        <v>0.8525590162679112</v>
       </c>
       <c r="U16">
         <v>0.0518</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>12.19706278087282</v>
+        <v>11.38392526214797</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0974799764672389</v>
+        <v>0.0972845906337105</v>
       </c>
       <c r="C17">
-        <v>12.54627470162347</v>
+        <v>12.41062387766645</v>
       </c>
       <c r="D17">
-        <v>11.34387470162346</v>
+        <v>11.35406387766645</v>
       </c>
       <c r="E17">
-        <v>1.5036</v>
+        <v>1.64944</v>
       </c>
       <c r="F17">
-        <v>2.1876</v>
+        <v>2.33344</v>
       </c>
       <c r="G17">
         <v>3.39</v>
@@ -2675,28 +2675,28 @@
         <v>1.29</v>
       </c>
       <c r="M17">
-        <v>0.11331768</v>
+        <v>0.120872192</v>
       </c>
       <c r="N17">
-        <v>1.17668232</v>
+        <v>1.169127808</v>
       </c>
       <c r="O17">
-        <v>0.2824037568</v>
+        <v>0.2805906739199999</v>
       </c>
       <c r="P17">
-        <v>0.8942785631999999</v>
+        <v>0.8885371340799999</v>
       </c>
       <c r="Q17">
-        <v>2.6942785632</v>
+        <v>2.68853713408</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1077350311379281</v>
+        <v>0.1083163221829887</v>
       </c>
       <c r="T17">
-        <v>0.8525590162679111</v>
+        <v>0.8605607063040158</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>11.38392526214797</v>
+        <v>10.67242993326372</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.0972845906337105</v>
+        <v>0.0970892048001821</v>
       </c>
       <c r="C18">
-        <v>12.41062387766645</v>
+        <v>12.27499137419454</v>
       </c>
       <c r="D18">
-        <v>11.35406387766645</v>
+        <v>11.36427137419454</v>
       </c>
       <c r="E18">
-        <v>1.64944</v>
+        <v>1.79528</v>
       </c>
       <c r="F18">
-        <v>2.33344</v>
+        <v>2.47928</v>
       </c>
       <c r="G18">
         <v>3.39</v>
@@ -2757,28 +2757,28 @@
         <v>1.29</v>
       </c>
       <c r="M18">
-        <v>0.120872192</v>
+        <v>0.128426704</v>
       </c>
       <c r="N18">
-        <v>1.169127808</v>
+        <v>1.161573296</v>
       </c>
       <c r="O18">
-        <v>0.2805906739199999</v>
+        <v>0.2787775910399999</v>
       </c>
       <c r="P18">
-        <v>0.8885371340799999</v>
+        <v>0.8827957049599999</v>
       </c>
       <c r="Q18">
-        <v>2.68853713408</v>
+        <v>2.68279570496</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1083163221829887</v>
+        <v>0.1089116202411833</v>
       </c>
       <c r="T18">
-        <v>0.8605607063040158</v>
+        <v>0.8687552081482194</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>10.67242993326372</v>
+        <v>10.04463993718939</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0970892048001821</v>
+        <v>0.09712637896665371</v>
       </c>
       <c r="C19">
-        <v>12.27499137419454</v>
+        <v>12.12720787935159</v>
       </c>
       <c r="D19">
-        <v>11.36427137419454</v>
+        <v>11.36232787935159</v>
       </c>
       <c r="E19">
-        <v>1.79528</v>
+        <v>1.94112</v>
       </c>
       <c r="F19">
-        <v>2.47928</v>
+        <v>2.62512</v>
       </c>
       <c r="G19">
         <v>3.39</v>
@@ -2839,45 +2839,45 @@
         <v>1.29</v>
       </c>
       <c r="M19">
-        <v>0.128426704</v>
+        <v>0.14044392</v>
       </c>
       <c r="N19">
-        <v>1.161573296</v>
+        <v>1.14955608</v>
       </c>
       <c r="O19">
-        <v>0.2787775910399999</v>
+        <v>0.2758934591999999</v>
       </c>
       <c r="P19">
-        <v>0.8827957049599999</v>
+        <v>0.8736626207999998</v>
       </c>
       <c r="Q19">
-        <v>2.68279570496</v>
+        <v>2.6736626208</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1089116202411833</v>
+        <v>0.1095214377642119</v>
       </c>
       <c r="T19">
-        <v>0.8687552081482194</v>
+        <v>0.8771495758910621</v>
       </c>
       <c r="U19">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V19">
         <v>0.24</v>
       </c>
       <c r="W19">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y19">
-        <v>10.04463993718939</v>
+        <v>9.185160881296959</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09712637896665371</v>
+        <v>0.09694391313312534</v>
       </c>
       <c r="C20">
-        <v>12.12720787935159</v>
+        <v>11.99091371913433</v>
       </c>
       <c r="D20">
-        <v>11.36232787935159</v>
+        <v>11.37187371913433</v>
       </c>
       <c r="E20">
-        <v>1.94112</v>
+        <v>2.08696</v>
       </c>
       <c r="F20">
-        <v>2.62512</v>
+        <v>2.77096</v>
       </c>
       <c r="G20">
         <v>3.39</v>
@@ -2921,28 +2921,28 @@
         <v>1.29</v>
       </c>
       <c r="M20">
-        <v>0.14044392</v>
+        <v>0.14824636</v>
       </c>
       <c r="N20">
-        <v>1.14955608</v>
+        <v>1.14175364</v>
       </c>
       <c r="O20">
-        <v>0.2758934591999999</v>
+        <v>0.2740208736</v>
       </c>
       <c r="P20">
-        <v>0.8736626207999998</v>
+        <v>0.8677327663999999</v>
       </c>
       <c r="Q20">
-        <v>2.6736626208</v>
+        <v>2.6677327664</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1095214377642118</v>
+        <v>0.1101463125100313</v>
       </c>
       <c r="T20">
-        <v>0.877149575891062</v>
+        <v>0.8857512119732341</v>
       </c>
       <c r="U20">
         <v>0.0535</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>9.185160881296961</v>
+        <v>8.701731361228699</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09694391313312534</v>
+        <v>0.09676144729959693</v>
       </c>
       <c r="C21">
-        <v>11.99091371913433</v>
+        <v>11.85463561190863</v>
       </c>
       <c r="D21">
-        <v>11.37187371913433</v>
+        <v>11.38143561190863</v>
       </c>
       <c r="E21">
-        <v>2.08696</v>
+        <v>2.2328</v>
       </c>
       <c r="F21">
-        <v>2.77096</v>
+        <v>2.9168</v>
       </c>
       <c r="G21">
         <v>3.39</v>
@@ -3003,28 +3003,28 @@
         <v>1.29</v>
       </c>
       <c r="M21">
-        <v>0.14824636</v>
+        <v>0.1560488</v>
       </c>
       <c r="N21">
-        <v>1.14175364</v>
+        <v>1.1339512</v>
       </c>
       <c r="O21">
-        <v>0.2740208736</v>
+        <v>0.272148288</v>
       </c>
       <c r="P21">
-        <v>0.8677327663999999</v>
+        <v>0.8618029119999999</v>
       </c>
       <c r="Q21">
-        <v>2.6677327664</v>
+        <v>2.661802912</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1101463125100313</v>
+        <v>0.1107868091244961</v>
       </c>
       <c r="T21">
-        <v>0.8857512119732341</v>
+        <v>0.8945678889574606</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>8.701731361228699</v>
+        <v>8.266644793167263</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09676144729959693</v>
+        <v>0.09657898146606853</v>
       </c>
       <c r="C22">
-        <v>11.85463561190863</v>
+        <v>11.71837359820243</v>
       </c>
       <c r="D22">
-        <v>11.38143561190863</v>
+        <v>11.39101359820243</v>
       </c>
       <c r="E22">
-        <v>2.2328</v>
+        <v>2.37864</v>
       </c>
       <c r="F22">
-        <v>2.9168</v>
+        <v>3.06264</v>
       </c>
       <c r="G22">
         <v>3.39</v>
@@ -3085,28 +3085,28 @@
         <v>1.29</v>
       </c>
       <c r="M22">
-        <v>0.1560488</v>
+        <v>0.16385124</v>
       </c>
       <c r="N22">
-        <v>1.1339512</v>
+        <v>1.12614876</v>
       </c>
       <c r="O22">
-        <v>0.272148288</v>
+        <v>0.2702757023999999</v>
       </c>
       <c r="P22">
-        <v>0.8618029119999999</v>
+        <v>0.8558730575999998</v>
       </c>
       <c r="Q22">
-        <v>2.661802912</v>
+        <v>2.6558730576</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1107868091244961</v>
+        <v>0.1114435208431247</v>
       </c>
       <c r="T22">
-        <v>0.8945678889574606</v>
+        <v>0.903607772953946</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.266644793167263</v>
+        <v>7.87299504111168</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09657898146606853</v>
+        <v>0.09653027563254014</v>
       </c>
       <c r="C23">
-        <v>11.71837359820243</v>
+        <v>11.57509298855705</v>
       </c>
       <c r="D23">
-        <v>11.39101359820243</v>
+        <v>11.39357298855705</v>
       </c>
       <c r="E23">
-        <v>2.37864</v>
+        <v>2.52448</v>
       </c>
       <c r="F23">
-        <v>3.06264</v>
+        <v>3.20848</v>
       </c>
       <c r="G23">
         <v>3.39</v>
@@ -3167,45 +3167,45 @@
         <v>1.29</v>
       </c>
       <c r="M23">
-        <v>0.16385124</v>
+        <v>0.174220464</v>
       </c>
       <c r="N23">
-        <v>1.12614876</v>
+        <v>1.115779536</v>
       </c>
       <c r="O23">
-        <v>0.2702757023999999</v>
+        <v>0.2677870886399999</v>
       </c>
       <c r="P23">
-        <v>0.8558730575999998</v>
+        <v>0.8479924473599998</v>
       </c>
       <c r="Q23">
-        <v>2.6558730576</v>
+        <v>2.64799244736</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1114435208431247</v>
+        <v>0.1121170713237694</v>
       </c>
       <c r="T23">
-        <v>0.903607772953946</v>
+        <v>0.9128794488477772</v>
       </c>
       <c r="U23">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V23">
         <v>0.24</v>
       </c>
       <c r="W23">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y23">
-        <v>7.87299504111168</v>
+        <v>7.404411458805435</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09653027563254014</v>
+        <v>0.09635388979901174</v>
       </c>
       <c r="C24">
-        <v>11.57509298855705</v>
+        <v>11.43853132982515</v>
       </c>
       <c r="D24">
-        <v>11.39357298855705</v>
+        <v>11.40285132982515</v>
       </c>
       <c r="E24">
-        <v>2.52448</v>
+        <v>2.67032</v>
       </c>
       <c r="F24">
-        <v>3.20848</v>
+        <v>3.35432</v>
       </c>
       <c r="G24">
         <v>3.39</v>
@@ -3249,28 +3249,28 @@
         <v>1.29</v>
       </c>
       <c r="M24">
-        <v>0.174220464</v>
+        <v>0.182139576</v>
       </c>
       <c r="N24">
-        <v>1.115779536</v>
+        <v>1.107860424</v>
       </c>
       <c r="O24">
-        <v>0.2677870886399999</v>
+        <v>0.2658865017599999</v>
       </c>
       <c r="P24">
-        <v>0.8479924473599998</v>
+        <v>0.8419739222399999</v>
       </c>
       <c r="Q24">
-        <v>2.64799244736</v>
+        <v>2.64197392224</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1121170713237694</v>
+        <v>0.1128081166220932</v>
       </c>
       <c r="T24">
-        <v>0.9128794488477772</v>
+        <v>0.9223919474920974</v>
       </c>
       <c r="U24">
         <v>0.0543</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>7.404411458805435</v>
+        <v>7.082480525813895</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.09635388979901174</v>
+        <v>0.09617750396548333</v>
       </c>
       <c r="C25">
-        <v>11.43853132982515</v>
+        <v>11.30198479501956</v>
       </c>
       <c r="D25">
-        <v>11.40285132982515</v>
+        <v>11.41214479501956</v>
       </c>
       <c r="E25">
-        <v>2.67032</v>
+        <v>2.81616</v>
       </c>
       <c r="F25">
-        <v>3.35432</v>
+        <v>3.50016</v>
       </c>
       <c r="G25">
         <v>3.39</v>
@@ -3331,28 +3331,28 @@
         <v>1.29</v>
       </c>
       <c r="M25">
-        <v>0.182139576</v>
+        <v>0.190058688</v>
       </c>
       <c r="N25">
-        <v>1.107860424</v>
+        <v>1.099941312</v>
       </c>
       <c r="O25">
-        <v>0.2658865017599999</v>
+        <v>0.2639859148799999</v>
       </c>
       <c r="P25">
-        <v>0.8419739222399999</v>
+        <v>0.83595539712</v>
       </c>
       <c r="Q25">
-        <v>2.64197392224</v>
+        <v>2.63595539712</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1128081166220932</v>
+        <v>0.1135173473230044</v>
       </c>
       <c r="T25">
-        <v>0.9223919474920974</v>
+        <v>0.9321547750481103</v>
       </c>
       <c r="U25">
         <v>0.0543</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>7.082480525813895</v>
+        <v>6.787377170571649</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09617750396548333</v>
+        <v>0.09600111813195494</v>
       </c>
       <c r="C26">
-        <v>11.30198479501956</v>
+        <v>11.165453421149</v>
       </c>
       <c r="D26">
-        <v>11.41214479501956</v>
+        <v>11.421453421149</v>
       </c>
       <c r="E26">
-        <v>2.81616</v>
+        <v>2.962</v>
       </c>
       <c r="F26">
-        <v>3.50016</v>
+        <v>3.646</v>
       </c>
       <c r="G26">
         <v>3.39</v>
@@ -3413,28 +3413,28 @@
         <v>1.29</v>
       </c>
       <c r="M26">
-        <v>0.190058688</v>
+        <v>0.1979778</v>
       </c>
       <c r="N26">
-        <v>1.099941312</v>
+        <v>1.0920222</v>
       </c>
       <c r="O26">
-        <v>0.2639859148799999</v>
+        <v>0.262085328</v>
       </c>
       <c r="P26">
-        <v>0.83595539712</v>
+        <v>0.8299368719999998</v>
       </c>
       <c r="Q26">
-        <v>2.63595539712</v>
+        <v>2.629936872</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1135173473230044</v>
+        <v>0.1142454908426066</v>
       </c>
       <c r="T26">
-        <v>0.9321547750481103</v>
+        <v>0.9421779446722836</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>6.78737717057165</v>
+        <v>6.515882083748783</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09600111813195494</v>
+        <v>0.09582473229842654</v>
       </c>
       <c r="C27">
-        <v>11.165453421149</v>
+        <v>11.02893724534306</v>
       </c>
       <c r="D27">
-        <v>11.421453421149</v>
+        <v>11.43077724534306</v>
       </c>
       <c r="E27">
-        <v>2.962</v>
+        <v>3.10784</v>
       </c>
       <c r="F27">
-        <v>3.646</v>
+        <v>3.79184</v>
       </c>
       <c r="G27">
         <v>3.39</v>
@@ -3495,28 +3495,28 @@
         <v>1.29</v>
       </c>
       <c r="M27">
-        <v>0.1979778</v>
+        <v>0.205896912</v>
       </c>
       <c r="N27">
-        <v>1.0920222</v>
+        <v>1.084103088</v>
       </c>
       <c r="O27">
-        <v>0.262085328</v>
+        <v>0.26018474112</v>
       </c>
       <c r="P27">
-        <v>0.8299368719999998</v>
+        <v>0.8239183468799998</v>
       </c>
       <c r="Q27">
-        <v>2.629936872</v>
+        <v>2.62391834688</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1142454908426066</v>
+        <v>0.1149933139167926</v>
       </c>
       <c r="T27">
-        <v>0.9421779446722836</v>
+        <v>0.9524720107727856</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.515882083748783</v>
+        <v>6.265271234373829</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09582473229842654</v>
+        <v>0.09585354646489816</v>
       </c>
       <c r="C28">
-        <v>11.02893724534306</v>
+        <v>10.8815730770892</v>
       </c>
       <c r="D28">
-        <v>11.43077724534306</v>
+        <v>11.4292530770892</v>
       </c>
       <c r="E28">
-        <v>3.10784</v>
+        <v>3.25368</v>
       </c>
       <c r="F28">
-        <v>3.79184</v>
+        <v>3.93768</v>
       </c>
       <c r="G28">
         <v>3.39</v>
@@ -3577,45 +3577,45 @@
         <v>1.29</v>
       </c>
       <c r="M28">
-        <v>0.205896912</v>
+        <v>0.217753704</v>
       </c>
       <c r="N28">
-        <v>1.084103088</v>
+        <v>1.072246296</v>
       </c>
       <c r="O28">
-        <v>0.26018474112</v>
+        <v>0.25733911104</v>
       </c>
       <c r="P28">
-        <v>0.8239183468799998</v>
+        <v>0.8149071849599999</v>
       </c>
       <c r="Q28">
-        <v>2.62391834688</v>
+        <v>2.61490718496</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1149933139167926</v>
+        <v>0.115761625294381</v>
       </c>
       <c r="T28">
-        <v>0.9524720107727856</v>
+        <v>0.9630481060815208</v>
       </c>
       <c r="U28">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V28">
         <v>0.24</v>
       </c>
       <c r="W28">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y28">
-        <v>6.265271234373829</v>
+        <v>5.92412425737658</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09585354646489816</v>
+        <v>0.09568476063136974</v>
       </c>
       <c r="C29">
-        <v>10.8815730770892</v>
+        <v>10.74466704269021</v>
       </c>
       <c r="D29">
-        <v>11.4292530770892</v>
+        <v>11.43818704269021</v>
       </c>
       <c r="E29">
-        <v>3.25368</v>
+        <v>3.39952</v>
       </c>
       <c r="F29">
-        <v>3.93768</v>
+        <v>4.08352</v>
       </c>
       <c r="G29">
         <v>3.39</v>
@@ -3659,28 +3659,28 @@
         <v>1.29</v>
       </c>
       <c r="M29">
-        <v>0.217753704</v>
+        <v>0.225818656</v>
       </c>
       <c r="N29">
-        <v>1.072246296</v>
+        <v>1.064181344</v>
       </c>
       <c r="O29">
-        <v>0.25733911104</v>
+        <v>0.25540352256</v>
       </c>
       <c r="P29">
-        <v>0.8149071849599999</v>
+        <v>0.8087778214399999</v>
       </c>
       <c r="Q29">
-        <v>2.61490718496</v>
+        <v>2.60877782144</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.115761625294381</v>
+        <v>0.1165512786546802</v>
       </c>
       <c r="T29">
-        <v>0.9630481060815208</v>
+        <v>0.9739179818154987</v>
       </c>
       <c r="U29">
         <v>0.0553</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.92412425737658</v>
+        <v>5.712548391041703</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09568476063136974</v>
+        <v>0.09551597479784137</v>
       </c>
       <c r="C30">
-        <v>10.74466704269021</v>
+        <v>10.60777498613905</v>
       </c>
       <c r="D30">
-        <v>11.43818704269021</v>
+        <v>11.44713498613905</v>
       </c>
       <c r="E30">
-        <v>3.39952</v>
+        <v>3.545360000000001</v>
       </c>
       <c r="F30">
-        <v>4.08352</v>
+        <v>4.229360000000001</v>
       </c>
       <c r="G30">
         <v>3.39</v>
@@ -3741,28 +3741,28 @@
         <v>1.29</v>
       </c>
       <c r="M30">
-        <v>0.225818656</v>
+        <v>0.233883608</v>
       </c>
       <c r="N30">
-        <v>1.064181344</v>
+        <v>1.056116392</v>
       </c>
       <c r="O30">
-        <v>0.25540352256</v>
+        <v>0.25346793408</v>
       </c>
       <c r="P30">
-        <v>0.8087778214399999</v>
+        <v>0.8026484579199999</v>
       </c>
       <c r="Q30">
-        <v>2.60877782144</v>
+        <v>2.60264845792</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1165512786546802</v>
+        <v>0.1173631757716076</v>
       </c>
       <c r="T30">
-        <v>0.9739179818154987</v>
+        <v>0.9850940512321239</v>
       </c>
       <c r="U30">
         <v>0.0553</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>5.712548391041703</v>
+        <v>5.515563963764402</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.09551597479784137</v>
+        <v>0.09534718896431296</v>
       </c>
       <c r="C31">
-        <v>10.60777498613905</v>
+        <v>10.47089694026547</v>
       </c>
       <c r="D31">
-        <v>11.44713498613905</v>
+        <v>11.45609694026547</v>
       </c>
       <c r="E31">
-        <v>3.54536</v>
+        <v>3.691199999999999</v>
       </c>
       <c r="F31">
-        <v>4.22936</v>
+        <v>4.3752</v>
       </c>
       <c r="G31">
         <v>3.39</v>
@@ -3823,28 +3823,28 @@
         <v>1.29</v>
       </c>
       <c r="M31">
-        <v>0.233883608</v>
+        <v>0.24194856</v>
       </c>
       <c r="N31">
-        <v>1.056116392</v>
+        <v>1.04805144</v>
       </c>
       <c r="O31">
-        <v>0.25346793408</v>
+        <v>0.2515323455999999</v>
       </c>
       <c r="P31">
-        <v>0.8026484579199999</v>
+        <v>0.7965190943999999</v>
       </c>
       <c r="Q31">
-        <v>2.60264845792</v>
+        <v>2.5965190944</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1173631757716076</v>
+        <v>0.1181982699490185</v>
       </c>
       <c r="T31">
-        <v>0.9850940512321239</v>
+        <v>0.9965894369177952</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.515563963764404</v>
+        <v>5.331711831638923</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09534718896431296</v>
+        <v>0.09517840313078457</v>
       </c>
       <c r="C32">
-        <v>10.47089694026547</v>
+        <v>10.33403293800209</v>
       </c>
       <c r="D32">
-        <v>11.45609694026547</v>
+        <v>11.46507293800209</v>
       </c>
       <c r="E32">
-        <v>3.691199999999999</v>
+        <v>3.83704</v>
       </c>
       <c r="F32">
-        <v>4.3752</v>
+        <v>4.52104</v>
       </c>
       <c r="G32">
         <v>3.39</v>
@@ -3905,28 +3905,28 @@
         <v>1.29</v>
       </c>
       <c r="M32">
-        <v>0.24194856</v>
+        <v>0.250013512</v>
       </c>
       <c r="N32">
-        <v>1.04805144</v>
+        <v>1.039986488</v>
       </c>
       <c r="O32">
-        <v>0.2515323455999999</v>
+        <v>0.24959675712</v>
       </c>
       <c r="P32">
-        <v>0.7965190943999999</v>
+        <v>0.7903897308799999</v>
       </c>
       <c r="Q32">
-        <v>2.5965190944</v>
+        <v>2.59038973088</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1181982699490185</v>
+        <v>0.1190575697547603</v>
       </c>
       <c r="T32">
-        <v>0.9965894369177952</v>
+        <v>1.008418022188559</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.331711831638923</v>
+        <v>5.159721127392506</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09517840313078457</v>
+        <v>0.09500961729725617</v>
       </c>
       <c r="C33">
-        <v>10.33403293800209</v>
+        <v>10.19718301238485</v>
       </c>
       <c r="D33">
-        <v>11.46507293800209</v>
+        <v>11.47406301238485</v>
       </c>
       <c r="E33">
-        <v>3.83704</v>
+        <v>3.98288</v>
       </c>
       <c r="F33">
-        <v>4.52104</v>
+        <v>4.66688</v>
       </c>
       <c r="G33">
         <v>3.39</v>
@@ -3987,28 +3987,28 @@
         <v>1.29</v>
       </c>
       <c r="M33">
-        <v>0.250013512</v>
+        <v>0.258078464</v>
       </c>
       <c r="N33">
-        <v>1.039986488</v>
+        <v>1.031921536</v>
       </c>
       <c r="O33">
-        <v>0.24959675712</v>
+        <v>0.24766116864</v>
       </c>
       <c r="P33">
-        <v>0.7903897308799999</v>
+        <v>0.7842603673599998</v>
       </c>
       <c r="Q33">
-        <v>2.59038973088</v>
+        <v>2.58426036736</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1190575697547603</v>
+        <v>0.1199421430842003</v>
       </c>
       <c r="T33">
-        <v>1.008418022188559</v>
+        <v>1.020594507026109</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.159721127392506</v>
+        <v>4.99847984216149</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09500961729725617</v>
+        <v>0.09484083146372778</v>
       </c>
       <c r="C34">
-        <v>10.19718301238485</v>
+        <v>10.06034719655336</v>
       </c>
       <c r="D34">
-        <v>11.47406301238485</v>
+        <v>11.48306719655336</v>
       </c>
       <c r="E34">
-        <v>3.98288</v>
+        <v>4.12872</v>
       </c>
       <c r="F34">
-        <v>4.66688</v>
+        <v>4.81272</v>
       </c>
       <c r="G34">
         <v>3.39</v>
@@ -4069,28 +4069,28 @@
         <v>1.29</v>
       </c>
       <c r="M34">
-        <v>0.258078464</v>
+        <v>0.266143416</v>
       </c>
       <c r="N34">
-        <v>1.031921536</v>
+        <v>1.023856584</v>
       </c>
       <c r="O34">
-        <v>0.24766116864</v>
+        <v>0.2457255801599999</v>
       </c>
       <c r="P34">
-        <v>0.7842603673599998</v>
+        <v>0.7781310038399999</v>
       </c>
       <c r="Q34">
-        <v>2.58426036736</v>
+        <v>2.57813100384</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1199421430842003</v>
+        <v>0.1208531215876534</v>
       </c>
       <c r="T34">
-        <v>1.020594507026109</v>
+        <v>1.03313446902299</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.99847984216149</v>
+        <v>4.847010756035385</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09484083146372778</v>
+        <v>0.09467204563019938</v>
       </c>
       <c r="C35">
-        <v>10.06034719655336</v>
+        <v>9.923525523751357</v>
       </c>
       <c r="D35">
-        <v>11.48306719655336</v>
+        <v>11.49208552375136</v>
       </c>
       <c r="E35">
-        <v>4.12872</v>
+        <v>4.27456</v>
       </c>
       <c r="F35">
-        <v>4.81272</v>
+        <v>4.95856</v>
       </c>
       <c r="G35">
         <v>3.39</v>
@@ -4151,28 +4151,28 @@
         <v>1.29</v>
       </c>
       <c r="M35">
-        <v>0.266143416</v>
+        <v>0.274208368</v>
       </c>
       <c r="N35">
-        <v>1.023856584</v>
+        <v>1.015791632</v>
       </c>
       <c r="O35">
-        <v>0.2457255801599999</v>
+        <v>0.2437899916799999</v>
       </c>
       <c r="P35">
-        <v>0.7781310038399999</v>
+        <v>0.7720016403199998</v>
       </c>
       <c r="Q35">
-        <v>2.57813100384</v>
+        <v>2.57200164032</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1208531215876534</v>
+        <v>0.1217917055003021</v>
       </c>
       <c r="T35">
-        <v>1.03313446902299</v>
+        <v>1.046054429868261</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.847010756035385</v>
+        <v>4.70445161615199</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09467204563019938</v>
+        <v>0.09450325979667096</v>
       </c>
       <c r="C36">
-        <v>9.923525523751357</v>
+        <v>9.786718027327089</v>
       </c>
       <c r="D36">
-        <v>11.49208552375136</v>
+        <v>11.50111802732709</v>
       </c>
       <c r="E36">
-        <v>4.27456</v>
+        <v>4.4204</v>
       </c>
       <c r="F36">
-        <v>4.95856</v>
+        <v>5.1044</v>
       </c>
       <c r="G36">
         <v>3.39</v>
@@ -4233,28 +4233,28 @@
         <v>1.29</v>
       </c>
       <c r="M36">
-        <v>0.274208368</v>
+        <v>0.28227332</v>
       </c>
       <c r="N36">
-        <v>1.015791632</v>
+        <v>1.00772668</v>
       </c>
       <c r="O36">
-        <v>0.2437899916799999</v>
+        <v>0.2418544031999999</v>
       </c>
       <c r="P36">
-        <v>0.7720016403199998</v>
+        <v>0.7658722767999998</v>
       </c>
       <c r="Q36">
-        <v>2.57200164032</v>
+        <v>2.5658722768</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1217917055003021</v>
+        <v>0.1227591689179554</v>
       </c>
       <c r="T36">
-        <v>1.046054429868261</v>
+        <v>1.059371927970309</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>4.70445161615199</v>
+        <v>4.570038712833362</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09450325979667096</v>
+        <v>0.09501847396314259</v>
       </c>
       <c r="C37">
-        <v>9.786718027327089</v>
+        <v>9.613350927502136</v>
       </c>
       <c r="D37">
-        <v>11.50111802732709</v>
+        <v>11.47359092750214</v>
       </c>
       <c r="E37">
-        <v>4.4204</v>
+        <v>4.566240000000001</v>
       </c>
       <c r="F37">
-        <v>5.1044</v>
+        <v>5.250240000000001</v>
       </c>
       <c r="G37">
         <v>3.39</v>
@@ -4315,45 +4315,45 @@
         <v>1.29</v>
       </c>
       <c r="M37">
-        <v>0.28227332</v>
+        <v>0.3034638720000001</v>
       </c>
       <c r="N37">
-        <v>1.00772668</v>
+        <v>0.9865361279999998</v>
       </c>
       <c r="O37">
-        <v>0.2418544031999999</v>
+        <v>0.2367686707199999</v>
       </c>
       <c r="P37">
-        <v>0.7658722767999998</v>
+        <v>0.7497674572799998</v>
       </c>
       <c r="Q37">
-        <v>2.5658722768</v>
+        <v>2.54976745728</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1227591689179554</v>
+        <v>0.1237568655674103</v>
       </c>
       <c r="T37">
-        <v>1.059371927970309</v>
+        <v>1.073105597888046</v>
       </c>
       <c r="U37">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V37">
         <v>0.24</v>
       </c>
       <c r="W37">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y37">
-        <v>4.570038712833362</v>
+        <v>4.250917881915115</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09501847396314259</v>
+        <v>0.09486868812961419</v>
       </c>
       <c r="C38">
-        <v>9.613350927502138</v>
+        <v>9.475500158975299</v>
       </c>
       <c r="D38">
-        <v>11.47359092750214</v>
+        <v>11.4815801589753</v>
       </c>
       <c r="E38">
-        <v>4.56624</v>
+        <v>4.712079999999999</v>
       </c>
       <c r="F38">
-        <v>5.25024</v>
+        <v>5.39608</v>
       </c>
       <c r="G38">
         <v>3.39</v>
@@ -4397,28 +4397,28 @@
         <v>1.29</v>
       </c>
       <c r="M38">
-        <v>0.303463872</v>
+        <v>0.311893424</v>
       </c>
       <c r="N38">
-        <v>0.9865361279999998</v>
+        <v>0.9781065759999998</v>
       </c>
       <c r="O38">
-        <v>0.2367686707199999</v>
+        <v>0.2347455782399999</v>
       </c>
       <c r="P38">
-        <v>0.7497674572799998</v>
+        <v>0.7433609977599999</v>
       </c>
       <c r="Q38">
-        <v>2.54976745728</v>
+        <v>2.54336099776</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1237568655674103</v>
+        <v>0.1247862351263717</v>
       </c>
       <c r="T38">
-        <v>1.073105597888046</v>
+        <v>1.087275257326981</v>
       </c>
       <c r="U38">
         <v>0.0578</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.250917881915115</v>
+        <v>4.136028209430924</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09486868812961419</v>
+        <v>0.09471890229608579</v>
       </c>
       <c r="C39">
-        <v>9.475500158975299</v>
+        <v>9.337660524241738</v>
       </c>
       <c r="D39">
-        <v>11.4815801589753</v>
+        <v>11.48958052424174</v>
       </c>
       <c r="E39">
-        <v>4.712079999999999</v>
+        <v>4.85792</v>
       </c>
       <c r="F39">
-        <v>5.39608</v>
+        <v>5.54192</v>
       </c>
       <c r="G39">
         <v>3.39</v>
@@ -4479,28 +4479,28 @@
         <v>1.29</v>
       </c>
       <c r="M39">
-        <v>0.311893424</v>
+        <v>0.320322976</v>
       </c>
       <c r="N39">
-        <v>0.9781065759999998</v>
+        <v>0.9696770239999998</v>
       </c>
       <c r="O39">
-        <v>0.2347455782399999</v>
+        <v>0.2327224857599999</v>
       </c>
       <c r="P39">
-        <v>0.7433609977599999</v>
+        <v>0.7369545382399998</v>
       </c>
       <c r="Q39">
-        <v>2.54336099776</v>
+        <v>2.53695453824</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1247862351263717</v>
+        <v>0.1258488101549771</v>
       </c>
       <c r="T39">
-        <v>1.087275257326981</v>
+        <v>1.10190200255427</v>
       </c>
       <c r="U39">
         <v>0.0578</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.136028209430924</v>
+        <v>4.02718536181432</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09471890229608579</v>
+        <v>0.0956065164625574</v>
       </c>
       <c r="C40">
-        <v>9.337660524241738</v>
+        <v>9.144573307249455</v>
       </c>
       <c r="D40">
-        <v>11.48958052424174</v>
+        <v>11.44233330724946</v>
       </c>
       <c r="E40">
-        <v>4.85792</v>
+        <v>5.00376</v>
       </c>
       <c r="F40">
-        <v>5.54192</v>
+        <v>5.68776</v>
       </c>
       <c r="G40">
         <v>3.39</v>
@@ -4561,45 +4561,45 @@
         <v>1.29</v>
       </c>
       <c r="M40">
-        <v>0.320322976</v>
+        <v>0.348659688</v>
       </c>
       <c r="N40">
-        <v>0.9696770239999998</v>
+        <v>0.9413403119999998</v>
       </c>
       <c r="O40">
-        <v>0.2327224857599999</v>
+        <v>0.22592167488</v>
       </c>
       <c r="P40">
-        <v>0.7369545382399998</v>
+        <v>0.7154186371199999</v>
       </c>
       <c r="Q40">
-        <v>2.53695453824</v>
+        <v>2.51541863712</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1258488101549771</v>
+        <v>0.1269462237091105</v>
       </c>
       <c r="T40">
-        <v>1.10190200255427</v>
+        <v>1.117008313198846</v>
       </c>
       <c r="U40">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V40">
         <v>0.24</v>
       </c>
       <c r="W40">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y40">
-        <v>4.02718536181432</v>
+        <v>3.699882849662849</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.0956065164625574</v>
+        <v>0.09548333062902901</v>
       </c>
       <c r="C41">
-        <v>9.144573307249455</v>
+        <v>9.005267186705344</v>
       </c>
       <c r="D41">
-        <v>11.44233330724946</v>
+        <v>11.44886718670534</v>
       </c>
       <c r="E41">
-        <v>5.00376</v>
+        <v>5.1496</v>
       </c>
       <c r="F41">
-        <v>5.68776</v>
+        <v>5.833600000000001</v>
       </c>
       <c r="G41">
         <v>3.39</v>
@@ -4643,28 +4643,28 @@
         <v>1.29</v>
       </c>
       <c r="M41">
-        <v>0.348659688</v>
+        <v>0.35759968</v>
       </c>
       <c r="N41">
-        <v>0.9413403119999998</v>
+        <v>0.9324003199999997</v>
       </c>
       <c r="O41">
-        <v>0.22592167488</v>
+        <v>0.2237760767999999</v>
       </c>
       <c r="P41">
-        <v>0.7154186371199999</v>
+        <v>0.7086242431999998</v>
       </c>
       <c r="Q41">
-        <v>2.51541863712</v>
+        <v>2.5086242432</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1269462237091105</v>
+        <v>0.1280802177150484</v>
       </c>
       <c r="T41">
-        <v>1.117008313198846</v>
+        <v>1.132618167531575</v>
       </c>
       <c r="U41">
         <v>0.0613</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.699882849662849</v>
+        <v>3.607385778421277</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09548333062902901</v>
+        <v>0.09536014479550059</v>
       </c>
       <c r="C42">
-        <v>9.005267186705344</v>
+        <v>8.865968532465798</v>
       </c>
       <c r="D42">
-        <v>11.44886718670534</v>
+        <v>11.4554085324658</v>
       </c>
       <c r="E42">
-        <v>5.1496</v>
+        <v>5.29544</v>
       </c>
       <c r="F42">
-        <v>5.833600000000001</v>
+        <v>5.97944</v>
       </c>
       <c r="G42">
         <v>3.39</v>
@@ -4725,28 +4725,28 @@
         <v>1.29</v>
       </c>
       <c r="M42">
-        <v>0.35759968</v>
+        <v>0.366539672</v>
       </c>
       <c r="N42">
-        <v>0.9324003199999997</v>
+        <v>0.9234603279999998</v>
       </c>
       <c r="O42">
-        <v>0.2237760767999999</v>
+        <v>0.2216304787199999</v>
       </c>
       <c r="P42">
-        <v>0.7086242431999998</v>
+        <v>0.7018298492799998</v>
       </c>
       <c r="Q42">
-        <v>2.5086242432</v>
+        <v>2.50182984928</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1280802177150484</v>
+        <v>0.1292526521957637</v>
       </c>
       <c r="T42">
-        <v>1.132618167531575</v>
+        <v>1.148757169468803</v>
       </c>
       <c r="U42">
         <v>0.0613</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.607385778421277</v>
+        <v>3.519400759435392</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.09536014479550059</v>
+        <v>0.09613071896197223</v>
       </c>
       <c r="C43">
-        <v>8.865968532465798</v>
+        <v>8.679332358572021</v>
       </c>
       <c r="D43">
-        <v>11.4554085324658</v>
+        <v>11.41461235857202</v>
       </c>
       <c r="E43">
-        <v>5.29544</v>
+        <v>5.44128</v>
       </c>
       <c r="F43">
-        <v>5.97944</v>
+        <v>6.12528</v>
       </c>
       <c r="G43">
         <v>3.39</v>
@@ -4807,45 +4807,45 @@
         <v>1.29</v>
       </c>
       <c r="M43">
-        <v>0.366539672</v>
+        <v>0.392630448</v>
       </c>
       <c r="N43">
-        <v>0.9234603279999998</v>
+        <v>0.8973695519999998</v>
       </c>
       <c r="O43">
-        <v>0.2216304787199999</v>
+        <v>0.2153686924799999</v>
       </c>
       <c r="P43">
-        <v>0.7018298492799998</v>
+        <v>0.6820008595199999</v>
       </c>
       <c r="Q43">
-        <v>2.50182984928</v>
+        <v>2.48200085952</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1292526521957637</v>
+        <v>0.1304655154516763</v>
       </c>
       <c r="T43">
-        <v>1.148757169468803</v>
+        <v>1.165452688714211</v>
       </c>
       <c r="U43">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V43">
         <v>0.24</v>
       </c>
       <c r="W43">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y43">
-        <v>3.519400759435392</v>
+        <v>3.285532251945982</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.09613071896197223</v>
+        <v>0.09602881312844383</v>
       </c>
       <c r="C44">
-        <v>8.679332358572021</v>
+        <v>8.538870834238121</v>
       </c>
       <c r="D44">
-        <v>11.41461235857202</v>
+        <v>11.41999083423812</v>
       </c>
       <c r="E44">
-        <v>5.44128</v>
+        <v>5.58712</v>
       </c>
       <c r="F44">
-        <v>6.12528</v>
+        <v>6.27112</v>
       </c>
       <c r="G44">
         <v>3.39</v>
@@ -4889,28 +4889,28 @@
         <v>1.29</v>
       </c>
       <c r="M44">
-        <v>0.392630448</v>
+        <v>0.401978792</v>
       </c>
       <c r="N44">
-        <v>0.8973695519999998</v>
+        <v>0.8880212079999998</v>
       </c>
       <c r="O44">
-        <v>0.2153686924799999</v>
+        <v>0.21312508992</v>
       </c>
       <c r="P44">
-        <v>0.6820008595199999</v>
+        <v>0.6748961180799999</v>
       </c>
       <c r="Q44">
-        <v>2.48200085952</v>
+        <v>2.47489611808</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1304655154516762</v>
+        <v>0.1317209353130593</v>
       </c>
       <c r="T44">
-        <v>1.165452688714211</v>
+        <v>1.182734015652441</v>
       </c>
       <c r="U44">
         <v>0.0641</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.285532251945982</v>
+        <v>3.209124525156541</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.09602881312844383</v>
+        <v>0.09592690729491543</v>
       </c>
       <c r="C45">
-        <v>8.538870834238121</v>
+        <v>8.398414380884581</v>
       </c>
       <c r="D45">
-        <v>11.41999083423812</v>
+        <v>11.42537438088458</v>
       </c>
       <c r="E45">
-        <v>5.58712</v>
+        <v>5.732959999999999</v>
       </c>
       <c r="F45">
-        <v>6.27112</v>
+        <v>6.41696</v>
       </c>
       <c r="G45">
         <v>3.39</v>
@@ -4971,28 +4971,28 @@
         <v>1.29</v>
       </c>
       <c r="M45">
-        <v>0.401978792</v>
+        <v>0.411327136</v>
       </c>
       <c r="N45">
-        <v>0.8880212079999998</v>
+        <v>0.8786728639999999</v>
       </c>
       <c r="O45">
-        <v>0.21312508992</v>
+        <v>0.21088148736</v>
       </c>
       <c r="P45">
-        <v>0.6748961180799999</v>
+        <v>0.6677913766399999</v>
       </c>
       <c r="Q45">
-        <v>2.47489611808</v>
+        <v>2.46779137664</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1317209353130593</v>
+        <v>0.1330211915980632</v>
       </c>
       <c r="T45">
-        <v>1.182734015652441</v>
+        <v>1.200632532838464</v>
       </c>
       <c r="U45">
         <v>0.0641</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.209124525156541</v>
+        <v>3.136189876857529</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.09592690729491543</v>
+        <v>0.09582500146138703</v>
       </c>
       <c r="C46">
-        <v>8.398414380884581</v>
+        <v>8.257963005686385</v>
       </c>
       <c r="D46">
-        <v>11.42537438088458</v>
+        <v>11.43076300568639</v>
       </c>
       <c r="E46">
-        <v>5.732959999999999</v>
+        <v>5.8788</v>
       </c>
       <c r="F46">
-        <v>6.41696</v>
+        <v>6.5628</v>
       </c>
       <c r="G46">
         <v>3.39</v>
@@ -5053,28 +5053,28 @@
         <v>1.29</v>
       </c>
       <c r="M46">
-        <v>0.411327136</v>
+        <v>0.42067548</v>
       </c>
       <c r="N46">
-        <v>0.8786728639999999</v>
+        <v>0.8693245199999997</v>
       </c>
       <c r="O46">
-        <v>0.21088148736</v>
+        <v>0.2086378847999999</v>
       </c>
       <c r="P46">
-        <v>0.6677913766399999</v>
+        <v>0.6606866351999998</v>
       </c>
       <c r="Q46">
-        <v>2.46779137664</v>
+        <v>2.4606866352</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1330211915980632</v>
+        <v>0.1343687299297946</v>
       </c>
       <c r="T46">
-        <v>1.200632532838464</v>
+        <v>1.219181905194889</v>
       </c>
       <c r="U46">
         <v>0.0641</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>3.136189876857529</v>
+        <v>3.066496768482916</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09582500146138703</v>
+        <v>0.09844997562785864</v>
       </c>
       <c r="C47">
-        <v>8.257963005686385</v>
+        <v>7.974919771509945</v>
       </c>
       <c r="D47">
-        <v>11.43076300568639</v>
+        <v>11.29355977150994</v>
       </c>
       <c r="E47">
-        <v>5.8788</v>
+        <v>6.02464</v>
       </c>
       <c r="F47">
-        <v>6.5628</v>
+        <v>6.70864</v>
       </c>
       <c r="G47">
         <v>3.39</v>
@@ -5135,45 +5135,45 @@
         <v>1.29</v>
       </c>
       <c r="M47">
-        <v>0.42067548</v>
+        <v>0.482351216</v>
       </c>
       <c r="N47">
-        <v>0.8693245199999997</v>
+        <v>0.8076487839999997</v>
       </c>
       <c r="O47">
-        <v>0.2086378847999999</v>
+        <v>0.1938357081599999</v>
       </c>
       <c r="P47">
-        <v>0.6606866351999998</v>
+        <v>0.6138130758399998</v>
       </c>
       <c r="Q47">
-        <v>2.4606866352</v>
+        <v>2.41381307584</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1343687299297946</v>
+        <v>0.1357661770886271</v>
       </c>
       <c r="T47">
-        <v>1.219181905194889</v>
+        <v>1.238418291342292</v>
       </c>
       <c r="U47">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V47">
         <v>0.24</v>
       </c>
       <c r="W47">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y47">
-        <v>3.066496768482916</v>
+        <v>2.674399809121658</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09844997562785864</v>
+        <v>0.09840734979433023</v>
       </c>
       <c r="C48">
-        <v>7.974919771509945</v>
+        <v>7.831281442858877</v>
       </c>
       <c r="D48">
-        <v>11.29355977150994</v>
+        <v>11.29576144285888</v>
       </c>
       <c r="E48">
-        <v>6.02464</v>
+        <v>6.17048</v>
       </c>
       <c r="F48">
-        <v>6.70864</v>
+        <v>6.854480000000001</v>
       </c>
       <c r="G48">
         <v>3.39</v>
@@ -5217,28 +5217,28 @@
         <v>1.29</v>
       </c>
       <c r="M48">
-        <v>0.482351216</v>
+        <v>0.4928371120000001</v>
       </c>
       <c r="N48">
-        <v>0.8076487839999997</v>
+        <v>0.7971628879999997</v>
       </c>
       <c r="O48">
-        <v>0.1938357081599999</v>
+        <v>0.1913190931199999</v>
       </c>
       <c r="P48">
-        <v>0.6138130758399998</v>
+        <v>0.6058437948799997</v>
       </c>
       <c r="Q48">
-        <v>2.41381307584</v>
+        <v>2.40584379488</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1357661770886271</v>
+        <v>0.1372163581025099</v>
       </c>
       <c r="T48">
-        <v>1.238418291342292</v>
+        <v>1.258380578853748</v>
       </c>
       <c r="U48">
         <v>0.07190000000000001</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.674399809121658</v>
+        <v>2.617497685523325</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09840734979433023</v>
+        <v>0.09836472396080184</v>
       </c>
       <c r="C49">
-        <v>7.831281442858877</v>
+        <v>7.687643972803681</v>
       </c>
       <c r="D49">
-        <v>11.29576144285888</v>
+        <v>11.29796397280368</v>
       </c>
       <c r="E49">
-        <v>6.17048</v>
+        <v>6.31632</v>
       </c>
       <c r="F49">
-        <v>6.854480000000001</v>
+        <v>7.00032</v>
       </c>
       <c r="G49">
         <v>3.39</v>
@@ -5299,28 +5299,28 @@
         <v>1.29</v>
       </c>
       <c r="M49">
-        <v>0.4928371120000001</v>
+        <v>0.5033230080000001</v>
       </c>
       <c r="N49">
-        <v>0.7971628879999997</v>
+        <v>0.7866769919999997</v>
       </c>
       <c r="O49">
-        <v>0.1913190931199999</v>
+        <v>0.1888024780799999</v>
       </c>
       <c r="P49">
-        <v>0.6058437948799997</v>
+        <v>0.5978745139199998</v>
       </c>
       <c r="Q49">
-        <v>2.40584379488</v>
+        <v>2.39787451392</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1372163581025099</v>
+        <v>0.1387223153092343</v>
       </c>
       <c r="T49">
-        <v>1.258380578853748</v>
+        <v>1.279110646654106</v>
       </c>
       <c r="U49">
         <v>0.07190000000000001</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.617497685523325</v>
+        <v>2.562966483741589</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.09836472396080184</v>
+        <v>0.09832209812727345</v>
       </c>
       <c r="C50">
-        <v>7.687643972803682</v>
+        <v>7.544007361846701</v>
       </c>
       <c r="D50">
-        <v>11.29796397280368</v>
+        <v>11.3001673618467</v>
       </c>
       <c r="E50">
-        <v>6.316319999999999</v>
+        <v>6.46216</v>
       </c>
       <c r="F50">
-        <v>7.000319999999999</v>
+        <v>7.14616</v>
       </c>
       <c r="G50">
         <v>3.39</v>
@@ -5381,28 +5381,28 @@
         <v>1.29</v>
       </c>
       <c r="M50">
-        <v>0.503323008</v>
+        <v>0.513808904</v>
       </c>
       <c r="N50">
-        <v>0.7866769919999999</v>
+        <v>0.7761910959999998</v>
       </c>
       <c r="O50">
-        <v>0.1888024780799999</v>
+        <v>0.1862858630399999</v>
       </c>
       <c r="P50">
-        <v>0.5978745139199999</v>
+        <v>0.5899052329599999</v>
       </c>
       <c r="Q50">
-        <v>2.39787451392</v>
+        <v>2.38990523296</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1387223153092343</v>
+        <v>0.1402873296613205</v>
       </c>
       <c r="T50">
-        <v>1.279110646654106</v>
+        <v>1.300653658289773</v>
       </c>
       <c r="U50">
         <v>0.07190000000000001</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.562966483741589</v>
+        <v>2.510661045297883</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.09832209812727345</v>
+        <v>0.09976147229374505</v>
       </c>
       <c r="C51">
-        <v>7.544007361846701</v>
+        <v>7.324236459855484</v>
       </c>
       <c r="D51">
-        <v>11.3001673618467</v>
+        <v>11.22623645985548</v>
       </c>
       <c r="E51">
-        <v>6.46216</v>
+        <v>6.608</v>
       </c>
       <c r="F51">
-        <v>7.14616</v>
+        <v>7.292</v>
       </c>
       <c r="G51">
         <v>3.39</v>
@@ -5463,45 +5463,45 @@
         <v>1.29</v>
       </c>
       <c r="M51">
-        <v>0.513808904</v>
+        <v>0.5527336</v>
       </c>
       <c r="N51">
-        <v>0.7761910959999998</v>
+        <v>0.7372663999999998</v>
       </c>
       <c r="O51">
-        <v>0.1862858630399999</v>
+        <v>0.1769439359999999</v>
       </c>
       <c r="P51">
-        <v>0.5899052329599999</v>
+        <v>0.5603224639999999</v>
       </c>
       <c r="Q51">
-        <v>2.38990523296</v>
+        <v>2.360322464</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1402873296613205</v>
+        <v>0.1419149445874901</v>
       </c>
       <c r="T51">
-        <v>1.300653658289773</v>
+        <v>1.323058390390866</v>
       </c>
       <c r="U51">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V51">
         <v>0.24</v>
       </c>
       <c r="W51">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y51">
-        <v>2.510661045297883</v>
+        <v>2.333854862450916</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.09976147229374505</v>
+        <v>0.09974848646021667</v>
       </c>
       <c r="C52">
-        <v>7.324236459855484</v>
+        <v>7.179059129500287</v>
       </c>
       <c r="D52">
-        <v>11.22623645985548</v>
+        <v>11.22689912950029</v>
       </c>
       <c r="E52">
-        <v>6.608</v>
+        <v>6.753839999999999</v>
       </c>
       <c r="F52">
-        <v>7.292</v>
+        <v>7.43784</v>
       </c>
       <c r="G52">
         <v>3.39</v>
@@ -5545,28 +5545,28 @@
         <v>1.29</v>
       </c>
       <c r="M52">
-        <v>0.5527336</v>
+        <v>0.563788272</v>
       </c>
       <c r="N52">
-        <v>0.7372663999999998</v>
+        <v>0.7262117279999998</v>
       </c>
       <c r="O52">
-        <v>0.1769439359999999</v>
+        <v>0.1742908147199999</v>
       </c>
       <c r="P52">
-        <v>0.5603224639999999</v>
+        <v>0.5519209132799998</v>
       </c>
       <c r="Q52">
-        <v>2.360322464</v>
+        <v>2.35192091328</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1419149445874901</v>
+        <v>0.1436089927759524</v>
       </c>
       <c r="T52">
-        <v>1.323058390390866</v>
+        <v>1.346377601353228</v>
       </c>
       <c r="U52">
         <v>0.07580000000000001</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.333854862450916</v>
+        <v>2.288093002402859</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.09974848646021667</v>
+        <v>0.09973550062668828</v>
       </c>
       <c r="C53">
-        <v>7.179059129500287</v>
+        <v>7.033881877382702</v>
       </c>
       <c r="D53">
-        <v>11.22689912950029</v>
+        <v>11.2275618773827</v>
       </c>
       <c r="E53">
-        <v>6.753839999999999</v>
+        <v>6.89968</v>
       </c>
       <c r="F53">
-        <v>7.43784</v>
+        <v>7.58368</v>
       </c>
       <c r="G53">
         <v>3.39</v>
@@ -5627,28 +5627,28 @@
         <v>1.29</v>
       </c>
       <c r="M53">
-        <v>0.563788272</v>
+        <v>0.574842944</v>
       </c>
       <c r="N53">
-        <v>0.7262117279999998</v>
+        <v>0.7151570559999998</v>
       </c>
       <c r="O53">
-        <v>0.1742908147199999</v>
+        <v>0.1716376934399999</v>
       </c>
       <c r="P53">
-        <v>0.5519209132799998</v>
+        <v>0.5435193625599999</v>
       </c>
       <c r="Q53">
-        <v>2.35192091328</v>
+        <v>2.34351936256</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1436089927759524</v>
+        <v>0.1453736263056006</v>
       </c>
       <c r="T53">
-        <v>1.346377601353228</v>
+        <v>1.370668446105689</v>
       </c>
       <c r="U53">
         <v>0.07580000000000001</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.288093002402859</v>
+        <v>2.244091213895111</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09973550062668828</v>
+        <v>0.09972251479315986</v>
       </c>
       <c r="C54">
-        <v>7.033881877382702</v>
+        <v>6.888704703516589</v>
       </c>
       <c r="D54">
-        <v>11.2275618773827</v>
+        <v>11.22822470351659</v>
       </c>
       <c r="E54">
-        <v>6.89968</v>
+        <v>7.04552</v>
       </c>
       <c r="F54">
-        <v>7.58368</v>
+        <v>7.72952</v>
       </c>
       <c r="G54">
         <v>3.39</v>
@@ -5709,28 +5709,28 @@
         <v>1.29</v>
       </c>
       <c r="M54">
-        <v>0.574842944</v>
+        <v>0.585897616</v>
       </c>
       <c r="N54">
-        <v>0.7151570559999998</v>
+        <v>0.7041023839999998</v>
       </c>
       <c r="O54">
-        <v>0.1716376934399999</v>
+        <v>0.16898457216</v>
       </c>
       <c r="P54">
-        <v>0.5435193625599999</v>
+        <v>0.5351178118399998</v>
       </c>
       <c r="Q54">
-        <v>2.34351936256</v>
+        <v>2.33511781184</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1453736263056006</v>
+        <v>0.1472133506237444</v>
       </c>
       <c r="T54">
-        <v>1.370668446105689</v>
+        <v>1.395992943826339</v>
       </c>
       <c r="U54">
         <v>0.07580000000000001</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.244091213895111</v>
+        <v>2.201749870236713</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09972251479315986</v>
+        <v>0.09970952895963148</v>
       </c>
       <c r="C55">
-        <v>6.888704703516589</v>
+        <v>6.743527607915803</v>
       </c>
       <c r="D55">
-        <v>11.22822470351659</v>
+        <v>11.2288876079158</v>
       </c>
       <c r="E55">
-        <v>7.04552</v>
+        <v>7.19136</v>
       </c>
       <c r="F55">
-        <v>7.72952</v>
+        <v>7.875360000000001</v>
       </c>
       <c r="G55">
         <v>3.39</v>
@@ -5791,28 +5791,28 @@
         <v>1.29</v>
       </c>
       <c r="M55">
-        <v>0.585897616</v>
+        <v>0.5969522880000001</v>
       </c>
       <c r="N55">
-        <v>0.7041023839999998</v>
+        <v>0.6930477119999997</v>
       </c>
       <c r="O55">
-        <v>0.16898457216</v>
+        <v>0.1663314508799999</v>
       </c>
       <c r="P55">
-        <v>0.5351178118399998</v>
+        <v>0.5267162611199998</v>
       </c>
       <c r="Q55">
-        <v>2.33511781184</v>
+        <v>2.32671626112</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1472133506237444</v>
+        <v>0.1491330629557206</v>
       </c>
       <c r="T55">
-        <v>1.395992943826339</v>
+        <v>1.422418506665279</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.201749870236713</v>
+        <v>2.160976724491589</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09970952895963148</v>
+        <v>0.09969654312610307</v>
       </c>
       <c r="C56">
-        <v>6.743527607915803</v>
+        <v>6.598350590594215</v>
       </c>
       <c r="D56">
-        <v>11.2288876079158</v>
+        <v>11.22955059059422</v>
       </c>
       <c r="E56">
-        <v>7.19136</v>
+        <v>7.3372</v>
       </c>
       <c r="F56">
-        <v>7.875360000000001</v>
+        <v>8.0212</v>
       </c>
       <c r="G56">
         <v>3.39</v>
@@ -5873,28 +5873,28 @@
         <v>1.29</v>
       </c>
       <c r="M56">
-        <v>0.5969522880000001</v>
+        <v>0.6080069600000001</v>
       </c>
       <c r="N56">
-        <v>0.6930477119999997</v>
+        <v>0.6819930399999997</v>
       </c>
       <c r="O56">
-        <v>0.1663314508799999</v>
+        <v>0.1636783295999999</v>
       </c>
       <c r="P56">
-        <v>0.5267162611199998</v>
+        <v>0.5183147103999998</v>
       </c>
       <c r="Q56">
-        <v>2.32671626112</v>
+        <v>2.3183147104</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1491330629557206</v>
+        <v>0.1511380958357846</v>
       </c>
       <c r="T56">
-        <v>1.422418506665279</v>
+        <v>1.450018538963727</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.160976724491589</v>
+        <v>2.121686238591742</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09969654312610307</v>
+        <v>0.09968355729257468</v>
       </c>
       <c r="C57">
-        <v>6.598350590594215</v>
+        <v>6.453173651565686</v>
       </c>
       <c r="D57">
-        <v>11.22955059059422</v>
+        <v>11.23021365156569</v>
       </c>
       <c r="E57">
-        <v>7.3372</v>
+        <v>7.48304</v>
       </c>
       <c r="F57">
-        <v>8.0212</v>
+        <v>8.16704</v>
       </c>
       <c r="G57">
         <v>3.39</v>
@@ -5955,28 +5955,28 @@
         <v>1.29</v>
       </c>
       <c r="M57">
-        <v>0.6080069600000001</v>
+        <v>0.6190616320000001</v>
       </c>
       <c r="N57">
-        <v>0.6819930399999997</v>
+        <v>0.6709383679999997</v>
       </c>
       <c r="O57">
-        <v>0.1636783295999999</v>
+        <v>0.1610252083199999</v>
       </c>
       <c r="P57">
-        <v>0.5183147103999998</v>
+        <v>0.5099131596799998</v>
       </c>
       <c r="Q57">
-        <v>2.3183147104</v>
+        <v>2.30991315968</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1511380958357846</v>
+        <v>0.1532342665740334</v>
       </c>
       <c r="T57">
-        <v>1.450018538963727</v>
+        <v>1.478873118184832</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.121686238591742</v>
+        <v>2.083798984331175</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09968355729257468</v>
+        <v>0.09967057145904629</v>
       </c>
       <c r="C58">
-        <v>6.453173651565686</v>
+        <v>6.307996790844088</v>
       </c>
       <c r="D58">
-        <v>11.23021365156569</v>
+        <v>11.23087679084409</v>
       </c>
       <c r="E58">
-        <v>7.48304</v>
+        <v>7.62888</v>
       </c>
       <c r="F58">
-        <v>8.16704</v>
+        <v>8.31288</v>
       </c>
       <c r="G58">
         <v>3.39</v>
@@ -6037,28 +6037,28 @@
         <v>1.29</v>
       </c>
       <c r="M58">
-        <v>0.6190616320000001</v>
+        <v>0.6301163040000001</v>
       </c>
       <c r="N58">
-        <v>0.6709383679999997</v>
+        <v>0.6598836959999997</v>
       </c>
       <c r="O58">
-        <v>0.1610252083199999</v>
+        <v>0.1583720870399999</v>
       </c>
       <c r="P58">
-        <v>0.5099131596799998</v>
+        <v>0.5015116089599998</v>
       </c>
       <c r="Q58">
-        <v>2.30991315968</v>
+        <v>2.30151160896</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1532342665740334</v>
+        <v>0.155427933625689</v>
       </c>
       <c r="T58">
-        <v>1.478873118184832</v>
+        <v>1.509069770858081</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.083798984331175</v>
+        <v>2.047241107413084</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09967057145904629</v>
+        <v>0.09965758562551788</v>
       </c>
       <c r="C59">
-        <v>6.307996790844088</v>
+        <v>6.162820008443289</v>
       </c>
       <c r="D59">
-        <v>11.23087679084409</v>
+        <v>11.23154000844329</v>
       </c>
       <c r="E59">
-        <v>7.62888</v>
+        <v>7.774720000000001</v>
       </c>
       <c r="F59">
-        <v>8.31288</v>
+        <v>8.458720000000001</v>
       </c>
       <c r="G59">
         <v>3.39</v>
@@ -6119,28 +6119,28 @@
         <v>1.29</v>
       </c>
       <c r="M59">
-        <v>0.6301163040000001</v>
+        <v>0.6411709760000002</v>
       </c>
       <c r="N59">
-        <v>0.6598836959999997</v>
+        <v>0.6488290239999996</v>
       </c>
       <c r="O59">
-        <v>0.1583720870399999</v>
+        <v>0.1557189657599999</v>
       </c>
       <c r="P59">
-        <v>0.5015116089599998</v>
+        <v>0.4931100582399998</v>
       </c>
       <c r="Q59">
-        <v>2.30151160896</v>
+        <v>2.29311005824</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.155427933625689</v>
+        <v>0.1577260610131378</v>
       </c>
       <c r="T59">
-        <v>1.509069770858081</v>
+        <v>1.540704359372914</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.047241107413084</v>
+        <v>2.011943846940444</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09965758562551788</v>
+        <v>0.1060118797919895</v>
       </c>
       <c r="C60">
-        <v>6.16282000844329</v>
+        <v>5.701546639712367</v>
       </c>
       <c r="D60">
-        <v>11.23154000844329</v>
+        <v>10.91610663971237</v>
       </c>
       <c r="E60">
-        <v>7.774719999999999</v>
+        <v>7.920559999999999</v>
       </c>
       <c r="F60">
-        <v>8.45872</v>
+        <v>8.604559999999999</v>
       </c>
       <c r="G60">
         <v>3.39</v>
@@ -6201,45 +6201,45 @@
         <v>1.29</v>
       </c>
       <c r="M60">
-        <v>0.6411709760000001</v>
+        <v>0.7744103999999999</v>
       </c>
       <c r="N60">
-        <v>0.6488290239999998</v>
+        <v>0.5155895999999999</v>
       </c>
       <c r="O60">
-        <v>0.1557189657599999</v>
+        <v>0.123741504</v>
       </c>
       <c r="P60">
-        <v>0.4931100582399998</v>
+        <v>0.3918480959999999</v>
       </c>
       <c r="Q60">
-        <v>2.29311005824</v>
+        <v>2.191848096</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1577260610131378</v>
+        <v>0.1601362921755841</v>
       </c>
       <c r="T60">
-        <v>1.540704359372914</v>
+        <v>1.573882098547006</v>
       </c>
       <c r="U60">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V60">
         <v>0.24</v>
       </c>
       <c r="W60">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y60">
-        <v>2.011943846940445</v>
+        <v>1.66578341406572</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1060118797919895</v>
+        <v>0.1061068139584611</v>
       </c>
       <c r="C61">
-        <v>5.701546639712367</v>
+        <v>5.551128288195262</v>
       </c>
       <c r="D61">
-        <v>10.91610663971237</v>
+        <v>10.91152828819526</v>
       </c>
       <c r="E61">
-        <v>7.920559999999999</v>
+        <v>8.0664</v>
       </c>
       <c r="F61">
-        <v>8.604559999999999</v>
+        <v>8.750399999999999</v>
       </c>
       <c r="G61">
         <v>3.39</v>
@@ -6283,28 +6283,28 @@
         <v>1.29</v>
       </c>
       <c r="M61">
-        <v>0.7744103999999999</v>
+        <v>0.7875359999999999</v>
       </c>
       <c r="N61">
-        <v>0.5155895999999999</v>
+        <v>0.5024639999999999</v>
       </c>
       <c r="O61">
-        <v>0.123741504</v>
+        <v>0.12059136</v>
       </c>
       <c r="P61">
-        <v>0.3918480959999999</v>
+        <v>0.3818726399999999</v>
       </c>
       <c r="Q61">
-        <v>2.191848096</v>
+        <v>2.18187264</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1601362921755841</v>
+        <v>0.1626670348961527</v>
       </c>
       <c r="T61">
-        <v>1.573882098547006</v>
+        <v>1.608718724679803</v>
       </c>
       <c r="U61">
         <v>0.09</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.66578341406572</v>
+        <v>1.638020357164625</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1061068139584611</v>
+        <v>0.1062017481249327</v>
       </c>
       <c r="C62">
-        <v>5.551128288195262</v>
+        <v>5.400713775503764</v>
       </c>
       <c r="D62">
-        <v>10.91152828819526</v>
+        <v>10.90695377550376</v>
       </c>
       <c r="E62">
-        <v>8.0664</v>
+        <v>8.21224</v>
       </c>
       <c r="F62">
-        <v>8.750399999999999</v>
+        <v>8.896239999999999</v>
       </c>
       <c r="G62">
         <v>3.39</v>
@@ -6365,28 +6365,28 @@
         <v>1.29</v>
       </c>
       <c r="M62">
-        <v>0.7875359999999999</v>
+        <v>0.8006615999999999</v>
       </c>
       <c r="N62">
-        <v>0.5024639999999999</v>
+        <v>0.4893384</v>
       </c>
       <c r="O62">
-        <v>0.12059136</v>
+        <v>0.117441216</v>
       </c>
       <c r="P62">
-        <v>0.3818726399999999</v>
+        <v>0.3718971839999999</v>
       </c>
       <c r="Q62">
-        <v>2.18187264</v>
+        <v>2.171897184</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1626670348961527</v>
+        <v>0.1653275592946993</v>
       </c>
       <c r="T62">
-        <v>1.608718724679803</v>
+        <v>1.645341844460436</v>
       </c>
       <c r="U62">
         <v>0.09</v>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.638020357164625</v>
+        <v>1.611167564424221</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1062017481249327</v>
+        <v>0.1062966822914043</v>
       </c>
       <c r="C63">
-        <v>5.400713775503764</v>
+        <v>5.25030309681177</v>
       </c>
       <c r="D63">
-        <v>10.90695377550376</v>
+        <v>10.90238309681177</v>
       </c>
       <c r="E63">
-        <v>8.21224</v>
+        <v>8.358080000000001</v>
       </c>
       <c r="F63">
-        <v>8.896239999999999</v>
+        <v>9.04208</v>
       </c>
       <c r="G63">
         <v>3.39</v>
@@ -6447,28 +6447,28 @@
         <v>1.29</v>
       </c>
       <c r="M63">
-        <v>0.8006615999999999</v>
+        <v>0.8137872</v>
       </c>
       <c r="N63">
-        <v>0.4893384</v>
+        <v>0.4762127999999998</v>
       </c>
       <c r="O63">
-        <v>0.117441216</v>
+        <v>0.1142910719999999</v>
       </c>
       <c r="P63">
-        <v>0.3718971839999999</v>
+        <v>0.3619217279999998</v>
       </c>
       <c r="Q63">
-        <v>2.171897184</v>
+        <v>2.161921728</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1653275592946993</v>
+        <v>0.1681281112931692</v>
       </c>
       <c r="T63">
-        <v>1.645341844460436</v>
+        <v>1.683892496861103</v>
       </c>
       <c r="U63">
         <v>0.09</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.611167564424221</v>
+        <v>1.585180990804475</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1062966822914043</v>
+        <v>0.1063916164578759</v>
       </c>
       <c r="C64">
-        <v>5.25030309681177</v>
+        <v>5.099896247301261</v>
       </c>
       <c r="D64">
-        <v>10.90238309681177</v>
+        <v>10.89781624730126</v>
       </c>
       <c r="E64">
-        <v>8.358080000000001</v>
+        <v>8.503920000000001</v>
       </c>
       <c r="F64">
-        <v>9.04208</v>
+        <v>9.18792</v>
       </c>
       <c r="G64">
         <v>3.39</v>
@@ -6529,28 +6529,28 @@
         <v>1.29</v>
       </c>
       <c r="M64">
-        <v>0.8137872</v>
+        <v>0.8269128</v>
       </c>
       <c r="N64">
-        <v>0.4762127999999998</v>
+        <v>0.4630871999999998</v>
       </c>
       <c r="O64">
-        <v>0.1142910719999999</v>
+        <v>0.1111409279999999</v>
       </c>
       <c r="P64">
-        <v>0.3619217279999998</v>
+        <v>0.3519462719999998</v>
       </c>
       <c r="Q64">
-        <v>2.161921728</v>
+        <v>2.151946272</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1681281112931692</v>
+        <v>0.1710800444807457</v>
       </c>
       <c r="T64">
-        <v>1.683892496861103</v>
+        <v>1.724526968310453</v>
       </c>
       <c r="U64">
         <v>0.09</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.585180990804475</v>
+        <v>1.560019387775833</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1063916164578759</v>
+        <v>0.1064865506243475</v>
       </c>
       <c r="C65">
-        <v>5.099896247301261</v>
+        <v>4.949493222162289</v>
       </c>
       <c r="D65">
-        <v>10.89781624730126</v>
+        <v>10.89325322216229</v>
       </c>
       <c r="E65">
-        <v>8.503920000000001</v>
+        <v>8.649760000000001</v>
       </c>
       <c r="F65">
-        <v>9.18792</v>
+        <v>9.33376</v>
       </c>
       <c r="G65">
         <v>3.39</v>
@@ -6611,28 +6611,28 @@
         <v>1.29</v>
       </c>
       <c r="M65">
-        <v>0.8269128</v>
+        <v>0.8400384</v>
       </c>
       <c r="N65">
-        <v>0.4630871999999998</v>
+        <v>0.4499615999999999</v>
       </c>
       <c r="O65">
-        <v>0.1111409279999999</v>
+        <v>0.107990784</v>
       </c>
       <c r="P65">
-        <v>0.3519462719999998</v>
+        <v>0.3419708159999999</v>
       </c>
       <c r="Q65">
-        <v>2.151946272</v>
+        <v>2.141970816</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1710800444807457</v>
+        <v>0.1741959739565209</v>
       </c>
       <c r="T65">
-        <v>1.724526968310453</v>
+        <v>1.767418910395879</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.560019387775833</v>
+        <v>1.535644084841836</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1064865506243475</v>
+        <v>0.1065814847908191</v>
       </c>
       <c r="C66">
-        <v>4.949493222162289</v>
+        <v>4.799094016592951</v>
       </c>
       <c r="D66">
-        <v>10.89325322216229</v>
+        <v>10.88869401659295</v>
       </c>
       <c r="E66">
-        <v>8.649760000000001</v>
+        <v>8.7956</v>
       </c>
       <c r="F66">
-        <v>9.33376</v>
+        <v>9.4796</v>
       </c>
       <c r="G66">
         <v>3.39</v>
@@ -6693,28 +6693,28 @@
         <v>1.29</v>
       </c>
       <c r="M66">
-        <v>0.8400384</v>
+        <v>0.8531639999999999</v>
       </c>
       <c r="N66">
-        <v>0.4499615999999999</v>
+        <v>0.4368359999999999</v>
       </c>
       <c r="O66">
-        <v>0.107990784</v>
+        <v>0.10484064</v>
       </c>
       <c r="P66">
-        <v>0.3419708159999999</v>
+        <v>0.3319953599999999</v>
       </c>
       <c r="Q66">
-        <v>2.141970816</v>
+        <v>2.13199536</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1741959739565209</v>
+        <v>0.1774899565451975</v>
       </c>
       <c r="T66">
-        <v>1.767418910395879</v>
+        <v>1.812761820600473</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.535644084841836</v>
+        <v>1.512018791228884</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1065814847908191</v>
+        <v>0.1379447591152853</v>
       </c>
       <c r="C67">
-        <v>4.799094016592951</v>
+        <v>3.330556206206182</v>
       </c>
       <c r="D67">
-        <v>10.88869401659295</v>
+        <v>9.565996206206181</v>
       </c>
       <c r="E67">
-        <v>8.7956</v>
+        <v>8.94144</v>
       </c>
       <c r="F67">
-        <v>9.4796</v>
+        <v>9.625439999999999</v>
       </c>
       <c r="G67">
         <v>3.39</v>
@@ -6775,45 +6775,45 @@
         <v>1.29</v>
       </c>
       <c r="M67">
-        <v>0.8531639999999999</v>
+        <v>1.413014592</v>
       </c>
       <c r="N67">
-        <v>0.4368359999999999</v>
+        <v>-0.1230145920000003</v>
       </c>
       <c r="O67">
-        <v>0.10484064</v>
+        <v>-0.02952350208000007</v>
       </c>
       <c r="P67">
-        <v>0.3319953599999999</v>
+        <v>-0.09349108992000024</v>
       </c>
       <c r="Q67">
-        <v>2.13199536</v>
+        <v>1.70650891008</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1774899565451975</v>
+        <v>0.1831926557180555</v>
       </c>
       <c r="T67">
-        <v>1.812761820600473</v>
+        <v>1.891261621239247</v>
       </c>
       <c r="U67">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V67">
-        <v>0.24</v>
+        <v>0.219106017554842</v>
       </c>
       <c r="W67">
-        <v>0.0684</v>
+        <v>0.1146352366229492</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y67">
-        <v>1.512018791228884</v>
+        <v>0.9129417398118418</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1379447591152853</v>
+        <v>0.1389547591152853</v>
       </c>
       <c r="C68">
-        <v>3.330556206206182</v>
+        <v>3.147441053501261</v>
       </c>
       <c r="D68">
-        <v>9.565996206206181</v>
+        <v>9.528721053501261</v>
       </c>
       <c r="E68">
-        <v>8.94144</v>
+        <v>9.087280000000002</v>
       </c>
       <c r="F68">
-        <v>9.625439999999999</v>
+        <v>9.771280000000001</v>
       </c>
       <c r="G68">
         <v>3.39</v>
@@ -6857,37 +6857,37 @@
         <v>1.29</v>
       </c>
       <c r="M68">
-        <v>1.413014592</v>
+        <v>1.434423904</v>
       </c>
       <c r="N68">
-        <v>-0.1230145920000003</v>
+        <v>-0.1444239040000004</v>
       </c>
       <c r="O68">
-        <v>-0.02952350208000007</v>
+        <v>-0.03466173696000009</v>
       </c>
       <c r="P68">
-        <v>-0.09349108992000024</v>
+        <v>-0.1097621670400003</v>
       </c>
       <c r="Q68">
-        <v>1.70650891008</v>
+        <v>1.69023783296</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1831926557180555</v>
+        <v>0.1873560695276935</v>
       </c>
       <c r="T68">
-        <v>1.891261621239247</v>
+        <v>1.948572579458618</v>
       </c>
       <c r="U68">
         <v>0.1468</v>
       </c>
       <c r="V68">
-        <v>0.219106017554842</v>
+        <v>0.2158357784868593</v>
       </c>
       <c r="W68">
-        <v>0.1146352366229492</v>
+        <v>0.1151153077181291</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.9129417398118418</v>
+        <v>0.899315743695247</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1389547591152853</v>
+        <v>0.1399647591152853</v>
       </c>
       <c r="C69">
-        <v>3.147441053501261</v>
+        <v>2.964615268233176</v>
       </c>
       <c r="D69">
-        <v>9.528721053501261</v>
+        <v>9.491735268233176</v>
       </c>
       <c r="E69">
-        <v>9.087280000000002</v>
+        <v>9.233120000000001</v>
       </c>
       <c r="F69">
-        <v>9.771280000000001</v>
+        <v>9.917120000000001</v>
       </c>
       <c r="G69">
         <v>3.39</v>
@@ -6939,37 +6939,37 @@
         <v>1.29</v>
       </c>
       <c r="M69">
-        <v>1.434423904</v>
+        <v>1.455833216</v>
       </c>
       <c r="N69">
-        <v>-0.1444239040000004</v>
+        <v>-0.1658332160000004</v>
       </c>
       <c r="O69">
-        <v>-0.03466173696000009</v>
+        <v>-0.03979997184000011</v>
       </c>
       <c r="P69">
-        <v>-0.1097621670400003</v>
+        <v>-0.1260332441600003</v>
       </c>
       <c r="Q69">
-        <v>1.69023783296</v>
+        <v>1.67396675584</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1873560695276935</v>
+        <v>0.1917796967004339</v>
       </c>
       <c r="T69">
-        <v>1.948572579458618</v>
+        <v>2.0094654725667</v>
       </c>
       <c r="U69">
         <v>0.1468</v>
       </c>
       <c r="V69">
-        <v>0.2158357784868593</v>
+        <v>0.212661722920876</v>
       </c>
       <c r="W69">
-        <v>0.1151153077181291</v>
+        <v>0.1155812590752154</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.899315743695247</v>
+        <v>0.8860905121703169</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1399647591152853</v>
+        <v>0.1409747591152853</v>
       </c>
       <c r="C70">
-        <v>2.964615268233176</v>
+        <v>2.782075493886177</v>
       </c>
       <c r="D70">
-        <v>9.491735268233176</v>
+        <v>9.455035493886177</v>
       </c>
       <c r="E70">
-        <v>9.233120000000001</v>
+        <v>9.378960000000001</v>
       </c>
       <c r="F70">
-        <v>9.917120000000001</v>
+        <v>10.06296</v>
       </c>
       <c r="G70">
         <v>3.39</v>
@@ -7021,37 +7021,37 @@
         <v>1.29</v>
       </c>
       <c r="M70">
-        <v>1.455833216</v>
+        <v>1.477242528</v>
       </c>
       <c r="N70">
-        <v>-0.1658332160000004</v>
+        <v>-0.1872425280000003</v>
       </c>
       <c r="O70">
-        <v>-0.03979997184000011</v>
+        <v>-0.04493820672000007</v>
       </c>
       <c r="P70">
-        <v>-0.1260332441600003</v>
+        <v>-0.1423043212800002</v>
       </c>
       <c r="Q70">
-        <v>1.67396675584</v>
+        <v>1.65769567872</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1917796967004339</v>
+        <v>0.1964887191746415</v>
       </c>
       <c r="T70">
-        <v>2.0094654725667</v>
+        <v>2.07428693942369</v>
       </c>
       <c r="U70">
         <v>0.1468</v>
       </c>
       <c r="V70">
-        <v>0.212661722920876</v>
+        <v>0.2095796689655011</v>
       </c>
       <c r="W70">
-        <v>0.1155812590752154</v>
+        <v>0.1160337045958645</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.8860905121703169</v>
+        <v>0.8732486206895878</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1409747591152853</v>
+        <v>0.1419847591152853</v>
       </c>
       <c r="C71">
-        <v>2.782075493886177</v>
+        <v>2.599818425656418</v>
       </c>
       <c r="D71">
-        <v>9.455035493886177</v>
+        <v>9.418618425656417</v>
       </c>
       <c r="E71">
-        <v>9.378960000000001</v>
+        <v>9.524800000000001</v>
       </c>
       <c r="F71">
-        <v>10.06296</v>
+        <v>10.2088</v>
       </c>
       <c r="G71">
         <v>3.39</v>
@@ -7103,37 +7103,37 @@
         <v>1.29</v>
       </c>
       <c r="M71">
-        <v>1.477242528</v>
+        <v>1.49865184</v>
       </c>
       <c r="N71">
-        <v>-0.1872425280000003</v>
+        <v>-0.2086518400000004</v>
       </c>
       <c r="O71">
-        <v>-0.04493820672000007</v>
+        <v>-0.05007644160000008</v>
       </c>
       <c r="P71">
-        <v>-0.1423043212800002</v>
+        <v>-0.1585753984000003</v>
       </c>
       <c r="Q71">
-        <v>1.65769567872</v>
+        <v>1.6414246016</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1964887191746415</v>
+        <v>0.2015116764804629</v>
       </c>
       <c r="T71">
-        <v>2.07428693942369</v>
+        <v>2.14342983740448</v>
       </c>
       <c r="U71">
         <v>0.1468</v>
       </c>
       <c r="V71">
-        <v>0.2095796689655011</v>
+        <v>0.2065856736945653</v>
       </c>
       <c r="W71">
-        <v>0.1160337045958645</v>
+        <v>0.1164732231016378</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.8732486206895878</v>
+        <v>0.8607736403940222</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1419847591152853</v>
+        <v>0.1429947591152854</v>
       </c>
       <c r="C72">
-        <v>2.599818425656418</v>
+        <v>2.417840809459895</v>
       </c>
       <c r="D72">
-        <v>9.418618425656417</v>
+        <v>9.382480809459896</v>
       </c>
       <c r="E72">
-        <v>9.524800000000001</v>
+        <v>9.670640000000002</v>
       </c>
       <c r="F72">
-        <v>10.2088</v>
+        <v>10.35464</v>
       </c>
       <c r="G72">
         <v>3.39</v>
@@ -7185,37 +7185,37 @@
         <v>1.29</v>
       </c>
       <c r="M72">
-        <v>1.49865184</v>
+        <v>1.520061152</v>
       </c>
       <c r="N72">
-        <v>-0.2086518400000004</v>
+        <v>-0.2300611520000007</v>
       </c>
       <c r="O72">
-        <v>-0.05007644160000008</v>
+        <v>-0.05521467648000015</v>
       </c>
       <c r="P72">
-        <v>-0.1585753984000003</v>
+        <v>-0.1748464755200005</v>
       </c>
       <c r="Q72">
-        <v>1.6414246016</v>
+        <v>1.62515352448</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2015116764804629</v>
+        <v>0.2068810446349617</v>
       </c>
       <c r="T72">
-        <v>2.14342983740448</v>
+        <v>2.217341211108083</v>
       </c>
       <c r="U72">
         <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.2065856736945653</v>
+        <v>0.2036760163185855</v>
       </c>
       <c r="W72">
-        <v>0.1164732231016378</v>
+        <v>0.1169003608044317</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8607736403940222</v>
+        <v>0.8486500679941062</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1429947591152853</v>
+        <v>0.1440047591152853</v>
       </c>
       <c r="C73">
-        <v>2.417840809459898</v>
+        <v>2.236139440963179</v>
       </c>
       <c r="D73">
-        <v>9.382480809459897</v>
+        <v>9.346619440963178</v>
       </c>
       <c r="E73">
-        <v>9.670640000000001</v>
+        <v>9.81648</v>
       </c>
       <c r="F73">
-        <v>10.35464</v>
+        <v>10.50048</v>
       </c>
       <c r="G73">
         <v>3.39</v>
@@ -7267,37 +7267,37 @@
         <v>1.29</v>
       </c>
       <c r="M73">
-        <v>1.520061152</v>
+        <v>1.541470464</v>
       </c>
       <c r="N73">
-        <v>-0.2300611520000002</v>
+        <v>-0.2514704640000003</v>
       </c>
       <c r="O73">
-        <v>-0.05521467648000005</v>
+        <v>-0.06035291136000007</v>
       </c>
       <c r="P73">
-        <v>-0.1748464755200002</v>
+        <v>-0.1911175526400002</v>
       </c>
       <c r="Q73">
-        <v>1.62515352448</v>
+        <v>1.60888244736</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2068810446349615</v>
+        <v>0.2126339390862102</v>
       </c>
       <c r="T73">
-        <v>2.217341211108082</v>
+        <v>2.296531968647657</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.2036760163185855</v>
+        <v>0.2008471827586052</v>
       </c>
       <c r="W73">
-        <v>0.1169003608044317</v>
+        <v>0.1173156335710368</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8486500679941065</v>
+        <v>0.8368632614941882</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1440047591152853</v>
+        <v>0.1450147591152853</v>
       </c>
       <c r="C74">
-        <v>2.236139440963179</v>
+        <v>2.05471116463622</v>
       </c>
       <c r="D74">
-        <v>9.346619440963178</v>
+        <v>9.311031164636219</v>
       </c>
       <c r="E74">
-        <v>9.81648</v>
+        <v>9.96232</v>
       </c>
       <c r="F74">
-        <v>10.50048</v>
+        <v>10.64632</v>
       </c>
       <c r="G74">
         <v>3.39</v>
@@ -7349,37 +7349,37 @@
         <v>1.29</v>
       </c>
       <c r="M74">
-        <v>1.541470464</v>
+        <v>1.562879776</v>
       </c>
       <c r="N74">
-        <v>-0.2514704640000003</v>
+        <v>-0.2728797760000001</v>
       </c>
       <c r="O74">
-        <v>-0.06035291136000007</v>
+        <v>-0.06549114624000003</v>
       </c>
       <c r="P74">
-        <v>-0.1911175526400002</v>
+        <v>-0.2073886297600001</v>
       </c>
       <c r="Q74">
-        <v>1.60888244736</v>
+        <v>1.59261137024</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2126339390862102</v>
+        <v>0.2188129738671809</v>
       </c>
       <c r="T74">
-        <v>2.296531968647657</v>
+        <v>2.381588708227199</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.2008471827586052</v>
+        <v>0.1980958514879394</v>
       </c>
       <c r="W74">
-        <v>0.1173156335710368</v>
+        <v>0.1177195290015705</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8368632614941882</v>
+        <v>0.8253993811997474</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1450147591152853</v>
+        <v>0.1460247591152853</v>
       </c>
       <c r="C75">
-        <v>2.05471116463622</v>
+        <v>1.873552872826783</v>
       </c>
       <c r="D75">
-        <v>9.311031164636219</v>
+        <v>9.275712872826782</v>
       </c>
       <c r="E75">
-        <v>9.96232</v>
+        <v>10.10816</v>
       </c>
       <c r="F75">
-        <v>10.64632</v>
+        <v>10.79216</v>
       </c>
       <c r="G75">
         <v>3.39</v>
@@ -7431,37 +7431,37 @@
         <v>1.29</v>
       </c>
       <c r="M75">
-        <v>1.562879776</v>
+        <v>1.584289088</v>
       </c>
       <c r="N75">
-        <v>-0.2728797760000001</v>
+        <v>-0.2942890880000002</v>
       </c>
       <c r="O75">
-        <v>-0.06549114624000003</v>
+        <v>-0.07062938112000004</v>
       </c>
       <c r="P75">
-        <v>-0.2073886297600001</v>
+        <v>-0.2236597068800001</v>
       </c>
       <c r="Q75">
-        <v>1.59261137024</v>
+        <v>1.57634029312</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2188129738671809</v>
+        <v>0.2254673190159187</v>
       </c>
       <c r="T75">
-        <v>2.381588708227199</v>
+        <v>2.473188273928245</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.1980958514879394</v>
+        <v>0.1954188805218861</v>
       </c>
       <c r="W75">
-        <v>0.1177195290015705</v>
+        <v>0.1181125083393871</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8253993811997474</v>
+        <v>0.8142453355078589</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1460247591152853</v>
+        <v>0.1470347591152853</v>
       </c>
       <c r="C76">
-        <v>1.873552872826783</v>
+        <v>1.692661504855824</v>
       </c>
       <c r="D76">
-        <v>9.275712872826782</v>
+        <v>9.240661504855822</v>
       </c>
       <c r="E76">
-        <v>10.10816</v>
+        <v>10.254</v>
       </c>
       <c r="F76">
-        <v>10.79216</v>
+        <v>10.938</v>
       </c>
       <c r="G76">
         <v>3.39</v>
@@ -7513,37 +7513,37 @@
         <v>1.29</v>
       </c>
       <c r="M76">
-        <v>1.584289088</v>
+        <v>1.6056984</v>
       </c>
       <c r="N76">
-        <v>-0.2942890880000002</v>
+        <v>-0.3156984000000003</v>
       </c>
       <c r="O76">
-        <v>-0.07062938112000004</v>
+        <v>-0.07576761600000007</v>
       </c>
       <c r="P76">
-        <v>-0.2236597068800001</v>
+        <v>-0.2399307840000002</v>
       </c>
       <c r="Q76">
-        <v>1.57634029312</v>
+        <v>1.560069216</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2254673190159187</v>
+        <v>0.2326540117765554</v>
       </c>
       <c r="T76">
-        <v>2.473188273928245</v>
+        <v>2.572115804885375</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.1954188805218861</v>
+        <v>0.192813295448261</v>
       </c>
       <c r="W76">
-        <v>0.1181125083393871</v>
+        <v>0.1184950082281953</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8142453355078589</v>
+        <v>0.8033887310344208</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1470347591152853</v>
+        <v>0.1912085245306509</v>
       </c>
       <c r="C77">
-        <v>1.692661504855824</v>
+        <v>0.2362030806716469</v>
       </c>
       <c r="D77">
-        <v>9.240661504855822</v>
+        <v>7.930043080671647</v>
       </c>
       <c r="E77">
-        <v>10.254</v>
+        <v>10.39984</v>
       </c>
       <c r="F77">
-        <v>10.938</v>
+        <v>11.08384</v>
       </c>
       <c r="G77">
         <v>3.39</v>
@@ -7595,45 +7595,45 @@
         <v>1.29</v>
       </c>
       <c r="M77">
-        <v>1.6056984</v>
+        <v>2.225635072</v>
       </c>
       <c r="N77">
-        <v>-0.3156984000000003</v>
+        <v>-0.9356350720000004</v>
       </c>
       <c r="O77">
-        <v>-0.07576761600000007</v>
+        <v>-0.2245524172800001</v>
       </c>
       <c r="P77">
-        <v>-0.2399307840000002</v>
+        <v>-0.7110826547200003</v>
       </c>
       <c r="Q77">
-        <v>1.560069216</v>
+        <v>1.08891734528</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2326540117765554</v>
+        <v>0.2492886181646017</v>
       </c>
       <c r="T77">
-        <v>2.572115804885375</v>
+        <v>2.801097423165564</v>
       </c>
       <c r="U77">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V77">
-        <v>0.192813295448261</v>
+        <v>0.1391063628961361</v>
       </c>
       <c r="W77">
-        <v>0.1184950082281953</v>
+        <v>0.1728674423304559</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y77">
-        <v>0.8033887310344208</v>
+        <v>0.5796098454005669</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1912085245306509</v>
+        <v>0.1927585245306509</v>
       </c>
       <c r="C78">
-        <v>0.2362030806716469</v>
+        <v>0.05109315826321215</v>
       </c>
       <c r="D78">
-        <v>7.930043080671647</v>
+        <v>7.890773158263213</v>
       </c>
       <c r="E78">
-        <v>10.39984</v>
+        <v>10.54568</v>
       </c>
       <c r="F78">
-        <v>11.08384</v>
+        <v>11.22968</v>
       </c>
       <c r="G78">
         <v>3.39</v>
@@ -7677,37 +7677,37 @@
         <v>1.29</v>
       </c>
       <c r="M78">
-        <v>2.225635072</v>
+        <v>2.254919744</v>
       </c>
       <c r="N78">
-        <v>-0.9356350720000004</v>
+        <v>-0.9649197440000001</v>
       </c>
       <c r="O78">
-        <v>-0.2245524172800001</v>
+        <v>-0.23158073856</v>
       </c>
       <c r="P78">
-        <v>-0.7110826547200003</v>
+        <v>-0.7333390054400001</v>
       </c>
       <c r="Q78">
-        <v>1.08891734528</v>
+        <v>1.06666099456</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2492886181646017</v>
+        <v>0.2581359493891496</v>
       </c>
       <c r="T78">
-        <v>2.801097423165564</v>
+        <v>2.922884267651023</v>
       </c>
       <c r="U78">
         <v>0.2008</v>
       </c>
       <c r="V78">
-        <v>0.1391063628961361</v>
+        <v>0.1372997867546278</v>
       </c>
       <c r="W78">
-        <v>0.1728674423304559</v>
+        <v>0.1732302028196707</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.5796098454005669</v>
+        <v>0.5720824448109493</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1927585245306509</v>
+        <v>0.1943085245306509</v>
       </c>
       <c r="C79">
-        <v>0.05109315826321215</v>
+        <v>-0.1336297478979329</v>
       </c>
       <c r="D79">
-        <v>7.890773158263213</v>
+        <v>7.851890252102066</v>
       </c>
       <c r="E79">
-        <v>10.54568</v>
+        <v>10.69152</v>
       </c>
       <c r="F79">
-        <v>11.22968</v>
+        <v>11.37552</v>
       </c>
       <c r="G79">
         <v>3.39</v>
@@ -7759,37 +7759,37 @@
         <v>1.29</v>
       </c>
       <c r="M79">
-        <v>2.254919744</v>
+        <v>2.284204416</v>
       </c>
       <c r="N79">
-        <v>-0.9649197440000001</v>
+        <v>-0.9942044160000003</v>
       </c>
       <c r="O79">
-        <v>-0.23158073856</v>
+        <v>-0.2386090598400001</v>
       </c>
       <c r="P79">
-        <v>-0.7333390054400001</v>
+        <v>-0.7555953561600003</v>
       </c>
       <c r="Q79">
-        <v>1.06666099456</v>
+        <v>1.04440464384</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2581359493891496</v>
+        <v>0.2677875834522928</v>
       </c>
       <c r="T79">
-        <v>2.922884267651023</v>
+        <v>3.055742643453343</v>
       </c>
       <c r="U79">
         <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1372997867546278</v>
+        <v>0.1355395330782864</v>
       </c>
       <c r="W79">
-        <v>0.1732302028196707</v>
+        <v>0.1735836617578801</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.5720824448109493</v>
+        <v>0.5647480544928601</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1943085245306509</v>
+        <v>0.1958585245306509</v>
       </c>
       <c r="C80">
-        <v>-0.1336297478979329</v>
+        <v>-0.3179713309905203</v>
       </c>
       <c r="D80">
-        <v>7.851890252102066</v>
+        <v>7.813388669009479</v>
       </c>
       <c r="E80">
-        <v>10.69152</v>
+        <v>10.83736</v>
       </c>
       <c r="F80">
-        <v>11.37552</v>
+        <v>11.52136</v>
       </c>
       <c r="G80">
         <v>3.39</v>
@@ -7841,37 +7841,37 @@
         <v>1.29</v>
       </c>
       <c r="M80">
-        <v>2.284204416</v>
+        <v>2.313489088</v>
       </c>
       <c r="N80">
-        <v>-0.9942044160000003</v>
+        <v>-1.023489088</v>
       </c>
       <c r="O80">
-        <v>-0.2386090598400001</v>
+        <v>-0.24563738112</v>
       </c>
       <c r="P80">
-        <v>-0.7555953561600003</v>
+        <v>-0.77785170688</v>
       </c>
       <c r="Q80">
-        <v>1.04440464384</v>
+        <v>1.02214829312</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2677875834522928</v>
+        <v>0.2783584207595449</v>
       </c>
       <c r="T80">
-        <v>3.055742643453343</v>
+        <v>3.201254197903503</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1355395330782864</v>
+        <v>0.1338238427861562</v>
       </c>
       <c r="W80">
-        <v>0.1735836617578801</v>
+        <v>0.1739281723685398</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.5647480544928601</v>
+        <v>0.5575993449423177</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1958585245306509</v>
+        <v>0.1974085245306509</v>
       </c>
       <c r="C81">
-        <v>-0.3179713309905203</v>
+        <v>-0.5019371730726281</v>
       </c>
       <c r="D81">
-        <v>7.813388669009479</v>
+        <v>7.775262826927373</v>
       </c>
       <c r="E81">
-        <v>10.83736</v>
+        <v>10.9832</v>
       </c>
       <c r="F81">
-        <v>11.52136</v>
+        <v>11.6672</v>
       </c>
       <c r="G81">
         <v>3.39</v>
@@ -7923,37 +7923,37 @@
         <v>1.29</v>
       </c>
       <c r="M81">
-        <v>2.313489088</v>
+        <v>2.34277376</v>
       </c>
       <c r="N81">
-        <v>-1.023489088</v>
+        <v>-1.052773760000001</v>
       </c>
       <c r="O81">
-        <v>-0.24563738112</v>
+        <v>-0.2526657024000001</v>
       </c>
       <c r="P81">
-        <v>-0.77785170688</v>
+        <v>-0.8001080576000006</v>
       </c>
       <c r="Q81">
-        <v>1.02214829312</v>
+        <v>0.9998919423999995</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2783584207595449</v>
+        <v>0.2899863417975221</v>
       </c>
       <c r="T81">
-        <v>3.201254197903503</v>
+        <v>3.361316907798678</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1338238427861562</v>
+        <v>0.1321510447513292</v>
       </c>
       <c r="W81">
-        <v>0.1739281723685398</v>
+        <v>0.1742640702139331</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.5575993449423177</v>
+        <v>0.5506293531305386</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1974085245306509</v>
+        <v>0.1989585245306509</v>
       </c>
       <c r="C82">
-        <v>-0.5019371730726281</v>
+        <v>-0.6855327477795896</v>
       </c>
       <c r="D82">
-        <v>7.775262826927373</v>
+        <v>7.737507252220411</v>
       </c>
       <c r="E82">
-        <v>10.9832</v>
+        <v>11.12904</v>
       </c>
       <c r="F82">
-        <v>11.6672</v>
+        <v>11.81304</v>
       </c>
       <c r="G82">
         <v>3.39</v>
@@ -8005,37 +8005,37 @@
         <v>1.29</v>
       </c>
       <c r="M82">
-        <v>2.34277376</v>
+        <v>2.372058432</v>
       </c>
       <c r="N82">
-        <v>-1.052773760000001</v>
+        <v>-1.082058432</v>
       </c>
       <c r="O82">
-        <v>-0.2526657024000001</v>
+        <v>-0.2596940236800001</v>
       </c>
       <c r="P82">
-        <v>-0.8001080576000006</v>
+        <v>-0.8223644083200004</v>
       </c>
       <c r="Q82">
-        <v>0.9998919423999995</v>
+        <v>0.9776355916799997</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2899863417975221</v>
+        <v>0.3028382545237075</v>
       </c>
       <c r="T82">
-        <v>3.361316907798678</v>
+        <v>3.538228323998608</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1321510447513292</v>
+        <v>0.1305195503716832</v>
       </c>
       <c r="W82">
-        <v>0.1742640702139331</v>
+        <v>0.174591674285366</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.5506293531305386</v>
+        <v>0.5438314598820134</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1989585245306509</v>
+        <v>0.2005085245306509</v>
       </c>
       <c r="C83">
-        <v>-0.6855327477795896</v>
+        <v>-0.8687634229437133</v>
       </c>
       <c r="D83">
-        <v>7.737507252220411</v>
+        <v>7.700116577056287</v>
       </c>
       <c r="E83">
-        <v>11.12904</v>
+        <v>11.27488</v>
       </c>
       <c r="F83">
-        <v>11.81304</v>
+        <v>11.95888</v>
       </c>
       <c r="G83">
         <v>3.39</v>
@@ -8087,37 +8087,37 @@
         <v>1.29</v>
       </c>
       <c r="M83">
-        <v>2.372058432</v>
+        <v>2.401343104</v>
       </c>
       <c r="N83">
-        <v>-1.082058432</v>
+        <v>-1.111343104000001</v>
       </c>
       <c r="O83">
-        <v>-0.2596940236800001</v>
+        <v>-0.2667223449600001</v>
       </c>
       <c r="P83">
-        <v>-0.8223644083200004</v>
+        <v>-0.8446207590400004</v>
       </c>
       <c r="Q83">
-        <v>0.9776355916799997</v>
+        <v>0.9553792409599996</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3028382545237075</v>
+        <v>0.3171181575528024</v>
       </c>
       <c r="T83">
-        <v>3.538228323998608</v>
+        <v>3.734796564220753</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1305195503716832</v>
+        <v>0.1289278485378822</v>
       </c>
       <c r="W83">
-        <v>0.174591674285366</v>
+        <v>0.1749112880135933</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5438314598820134</v>
+        <v>0.5371993689078425</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2005085245306509</v>
+        <v>0.2020585245306509</v>
       </c>
       <c r="C84">
-        <v>-0.8687634229437133</v>
+        <v>-1.051634463138408</v>
       </c>
       <c r="D84">
-        <v>7.700116577056287</v>
+        <v>7.663085536861593</v>
       </c>
       <c r="E84">
-        <v>11.27488</v>
+        <v>11.42072</v>
       </c>
       <c r="F84">
-        <v>11.95888</v>
+        <v>12.10472</v>
       </c>
       <c r="G84">
         <v>3.39</v>
@@ -8169,37 +8169,37 @@
         <v>1.29</v>
       </c>
       <c r="M84">
-        <v>2.401343104</v>
+        <v>2.430627776</v>
       </c>
       <c r="N84">
-        <v>-1.111343104000001</v>
+        <v>-1.140627776</v>
       </c>
       <c r="O84">
-        <v>-0.2667223449600001</v>
+        <v>-0.2737506662400001</v>
       </c>
       <c r="P84">
-        <v>-0.8446207590400004</v>
+        <v>-0.8668771097600003</v>
       </c>
       <c r="Q84">
-        <v>0.9553792409599996</v>
+        <v>0.9331228902399997</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3171181575528024</v>
+        <v>0.3330780491735554</v>
       </c>
       <c r="T84">
-        <v>3.734796564220753</v>
+        <v>3.95449047976315</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1289278485378822</v>
+        <v>0.1273745009651366</v>
       </c>
       <c r="W84">
-        <v>0.1749112880135933</v>
+        <v>0.1752232002062006</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.5371993689078425</v>
+        <v>0.5307270873547361</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2020585245306509</v>
+        <v>0.2036085245306509</v>
       </c>
       <c r="C85">
-        <v>-1.051634463138408</v>
+        <v>-1.234151032149214</v>
       </c>
       <c r="D85">
-        <v>7.663085536861593</v>
+        <v>7.626408967850787</v>
       </c>
       <c r="E85">
-        <v>11.42072</v>
+        <v>11.56656</v>
       </c>
       <c r="F85">
-        <v>12.10472</v>
+        <v>12.25056</v>
       </c>
       <c r="G85">
         <v>3.39</v>
@@ -8251,37 +8251,37 @@
         <v>1.29</v>
       </c>
       <c r="M85">
-        <v>2.430627776</v>
+        <v>2.459912448</v>
       </c>
       <c r="N85">
-        <v>-1.140627776</v>
+        <v>-1.169912448</v>
       </c>
       <c r="O85">
-        <v>-0.2737506662400001</v>
+        <v>-0.2807789875200001</v>
       </c>
       <c r="P85">
-        <v>-0.8668771097600003</v>
+        <v>-0.8891334604800003</v>
       </c>
       <c r="Q85">
-        <v>0.9331228902399997</v>
+        <v>0.9108665395199997</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3330780491735554</v>
+        <v>0.3510329272469027</v>
       </c>
       <c r="T85">
-        <v>3.95449047976315</v>
+        <v>4.201646134748348</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1273745009651366</v>
+        <v>0.1258581378584088</v>
       </c>
       <c r="W85">
-        <v>0.1752232002062006</v>
+        <v>0.1755276859180315</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5307270873547361</v>
+        <v>0.52440890774337</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2036085245306509</v>
+        <v>0.2051585245306509</v>
       </c>
       <c r="C86">
-        <v>-1.234151032149214</v>
+        <v>-1.416318195374252</v>
       </c>
       <c r="D86">
-        <v>7.626408967850787</v>
+        <v>7.590081804625747</v>
       </c>
       <c r="E86">
-        <v>11.56656</v>
+        <v>11.7124</v>
       </c>
       <c r="F86">
-        <v>12.25056</v>
+        <v>12.3964</v>
       </c>
       <c r="G86">
         <v>3.39</v>
@@ -8333,37 +8333,37 @@
         <v>1.29</v>
       </c>
       <c r="M86">
-        <v>2.459912448</v>
+        <v>2.48919712</v>
       </c>
       <c r="N86">
-        <v>-1.169912448</v>
+        <v>-1.19919712</v>
       </c>
       <c r="O86">
-        <v>-0.2807789875200001</v>
+        <v>-0.2878073088000001</v>
       </c>
       <c r="P86">
-        <v>-0.8891334604800003</v>
+        <v>-0.9113898112000002</v>
       </c>
       <c r="Q86">
-        <v>0.9108665395199997</v>
+        <v>0.8886101887999999</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3510329272469025</v>
+        <v>0.3713817890633627</v>
       </c>
       <c r="T86">
-        <v>4.201646134748345</v>
+        <v>4.481755877064902</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1258581378584088</v>
+        <v>0.124377453883604</v>
       </c>
       <c r="W86">
-        <v>0.1755276859180315</v>
+        <v>0.1758250072601723</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.52440890774337</v>
+        <v>0.5182393911816834</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2051585245306509</v>
+        <v>0.2067085245306509</v>
       </c>
       <c r="C87">
-        <v>-1.416318195374252</v>
+        <v>-1.59814092215638</v>
       </c>
       <c r="D87">
-        <v>7.590081804625747</v>
+        <v>7.554099077843619</v>
       </c>
       <c r="E87">
-        <v>11.7124</v>
+        <v>11.85824</v>
       </c>
       <c r="F87">
-        <v>12.3964</v>
+        <v>12.54224</v>
       </c>
       <c r="G87">
         <v>3.39</v>
@@ -8415,37 +8415,37 @@
         <v>1.29</v>
       </c>
       <c r="M87">
-        <v>2.48919712</v>
+        <v>2.518481792</v>
       </c>
       <c r="N87">
-        <v>-1.19919712</v>
+        <v>-1.228481792</v>
       </c>
       <c r="O87">
-        <v>-0.2878073088000001</v>
+        <v>-0.2948356300800001</v>
       </c>
       <c r="P87">
-        <v>-0.9113898112000002</v>
+        <v>-0.9336461619200003</v>
       </c>
       <c r="Q87">
-        <v>0.8886101887999999</v>
+        <v>0.8663538380799998</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3713817890633627</v>
+        <v>0.3946376311393171</v>
       </c>
       <c r="T87">
-        <v>4.481755877064902</v>
+        <v>4.801881296855251</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.124377453883604</v>
+        <v>0.1229312044198412</v>
       </c>
       <c r="W87">
-        <v>0.1758250072601723</v>
+        <v>0.1761154141524959</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5182393911816834</v>
+        <v>0.5122133517493382</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2067085245306509</v>
+        <v>0.2082585245306509</v>
       </c>
       <c r="C88">
-        <v>-1.59814092215638</v>
+        <v>-1.779624088049314</v>
       </c>
       <c r="D88">
-        <v>7.554099077843619</v>
+        <v>7.518455911950686</v>
       </c>
       <c r="E88">
-        <v>11.85824</v>
+        <v>12.00408</v>
       </c>
       <c r="F88">
-        <v>12.54224</v>
+        <v>12.68808</v>
       </c>
       <c r="G88">
         <v>3.39</v>
@@ -8497,37 +8497,37 @@
         <v>1.29</v>
       </c>
       <c r="M88">
-        <v>2.518481792</v>
+        <v>2.547766464</v>
       </c>
       <c r="N88">
-        <v>-1.228481792</v>
+        <v>-1.257766464</v>
       </c>
       <c r="O88">
-        <v>-0.2948356300800001</v>
+        <v>-0.30186395136</v>
       </c>
       <c r="P88">
-        <v>-0.9336461619200003</v>
+        <v>-0.95590251264</v>
       </c>
       <c r="Q88">
-        <v>0.8663538380799998</v>
+        <v>0.84409748736</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3946376311393171</v>
+        <v>0.4214712950731108</v>
       </c>
       <c r="T88">
-        <v>4.801881296855251</v>
+        <v>5.171256781228733</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1229312044198412</v>
+        <v>0.1215182020701878</v>
       </c>
       <c r="W88">
-        <v>0.1761154141524959</v>
+        <v>0.1763991450243063</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.5122133517493382</v>
+        <v>0.506325841959116</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2082585245306509</v>
+        <v>0.2098085245306509</v>
       </c>
       <c r="C89">
-        <v>-1.779624088049314</v>
+        <v>-1.960772477019901</v>
       </c>
       <c r="D89">
-        <v>7.518455911950686</v>
+        <v>7.483147522980097</v>
       </c>
       <c r="E89">
-        <v>12.00408</v>
+        <v>12.14992</v>
       </c>
       <c r="F89">
-        <v>12.68808</v>
+        <v>12.83392</v>
       </c>
       <c r="G89">
         <v>3.39</v>
@@ -8579,37 +8579,37 @@
         <v>1.29</v>
       </c>
       <c r="M89">
-        <v>2.547766464</v>
+        <v>2.577051136</v>
       </c>
       <c r="N89">
-        <v>-1.257766464</v>
+        <v>-1.287051136</v>
       </c>
       <c r="O89">
-        <v>-0.30186395136</v>
+        <v>-0.30889227264</v>
       </c>
       <c r="P89">
-        <v>-0.95590251264</v>
+        <v>-0.9781588633599999</v>
       </c>
       <c r="Q89">
-        <v>0.84409748736</v>
+        <v>0.8218411366400001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4214712950731108</v>
+        <v>0.4527772363292035</v>
       </c>
       <c r="T89">
-        <v>5.171256781228733</v>
+        <v>5.602194846331129</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1215182020701878</v>
+        <v>0.1201373134102994</v>
       </c>
       <c r="W89">
-        <v>0.1763991450243063</v>
+        <v>0.1766764274672119</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.506325841959116</v>
+        <v>0.5005721392095807</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2098085245306509</v>
+        <v>0.2433654895279924</v>
       </c>
       <c r="C90">
-        <v>-1.960772477019901</v>
+        <v>-2.797221618517051</v>
       </c>
       <c r="D90">
-        <v>7.483147522980097</v>
+        <v>6.792538381482949</v>
       </c>
       <c r="E90">
-        <v>12.14992</v>
+        <v>12.29576</v>
       </c>
       <c r="F90">
-        <v>12.83392</v>
+        <v>12.97976</v>
       </c>
       <c r="G90">
         <v>3.39</v>
@@ -8661,45 +8661,45 @@
         <v>1.29</v>
       </c>
       <c r="M90">
-        <v>2.577051136</v>
+        <v>3.060627408</v>
       </c>
       <c r="N90">
-        <v>-1.287051136</v>
+        <v>-1.770627408</v>
       </c>
       <c r="O90">
-        <v>-0.30889227264</v>
+        <v>-0.4249505779200001</v>
       </c>
       <c r="P90">
-        <v>-0.9781588633599999</v>
+        <v>-1.34567683008</v>
       </c>
       <c r="Q90">
-        <v>0.8218411366400001</v>
+        <v>0.4543231699199997</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4527772363292035</v>
+        <v>0.4975657577895079</v>
       </c>
       <c r="T90">
-        <v>5.602194846331129</v>
+        <v>6.218725702854869</v>
       </c>
       <c r="U90">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1201373134102994</v>
+        <v>0.1011557300933639</v>
       </c>
       <c r="W90">
-        <v>0.1766764274672119</v>
+        <v>0.2119474788439848</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y90">
-        <v>0.5005721392095807</v>
+        <v>0.4214822087223495</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2433654895279924</v>
+        <v>0.2452654895279923</v>
       </c>
       <c r="C91">
-        <v>-2.797221618517051</v>
+        <v>-2.978370795291575</v>
       </c>
       <c r="D91">
-        <v>6.792538381482949</v>
+        <v>6.757229204708426</v>
       </c>
       <c r="E91">
-        <v>12.29576</v>
+        <v>12.4416</v>
       </c>
       <c r="F91">
-        <v>12.97976</v>
+        <v>13.1256</v>
       </c>
       <c r="G91">
         <v>3.39</v>
@@ -8743,37 +8743,37 @@
         <v>1.29</v>
       </c>
       <c r="M91">
-        <v>3.060627408</v>
+        <v>3.09501648</v>
       </c>
       <c r="N91">
-        <v>-1.770627408</v>
+        <v>-1.805016480000001</v>
       </c>
       <c r="O91">
-        <v>-0.4249505779200001</v>
+        <v>-0.4332039552000001</v>
       </c>
       <c r="P91">
-        <v>-1.34567683008</v>
+        <v>-1.371812524800001</v>
       </c>
       <c r="Q91">
-        <v>0.4543231699199997</v>
+        <v>0.4281874751999994</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4975657577895079</v>
+        <v>0.5427423335684587</v>
       </c>
       <c r="T91">
-        <v>6.218725702854869</v>
+        <v>6.840598273140357</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1011557300933639</v>
+        <v>0.1000317775367709</v>
       </c>
       <c r="W91">
-        <v>0.2119474788439848</v>
+        <v>0.2122125068568294</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4214822087223495</v>
+        <v>0.416799073069879</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2452654895279923</v>
+        <v>0.2471654895279923</v>
       </c>
       <c r="C92">
-        <v>-2.978370795291575</v>
+        <v>-3.159154779974781</v>
       </c>
       <c r="D92">
-        <v>6.757229204708426</v>
+        <v>6.72228522002522</v>
       </c>
       <c r="E92">
-        <v>12.4416</v>
+        <v>12.58744</v>
       </c>
       <c r="F92">
-        <v>13.1256</v>
+        <v>13.27144</v>
       </c>
       <c r="G92">
         <v>3.39</v>
@@ -8825,37 +8825,37 @@
         <v>1.29</v>
       </c>
       <c r="M92">
-        <v>3.09501648</v>
+        <v>3.129405552</v>
       </c>
       <c r="N92">
-        <v>-1.805016480000001</v>
+        <v>-1.839405552</v>
       </c>
       <c r="O92">
-        <v>-0.4332039552000001</v>
+        <v>-0.4414573324800001</v>
       </c>
       <c r="P92">
-        <v>-1.371812524800001</v>
+        <v>-1.39794821952</v>
       </c>
       <c r="Q92">
-        <v>0.4281874751999994</v>
+        <v>0.4020517804799997</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5427423335684587</v>
+        <v>0.5979581484093985</v>
       </c>
       <c r="T92">
-        <v>6.840598273140357</v>
+        <v>7.60066474793373</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1000317775367709</v>
+        <v>0.09893252723416908</v>
       </c>
       <c r="W92">
-        <v>0.2122125068568294</v>
+        <v>0.2124717100781829</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.416799073069879</v>
+        <v>0.4122188634757046</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2471654895279923</v>
+        <v>0.2490654895279923</v>
       </c>
       <c r="C93">
-        <v>-3.159154779974781</v>
+        <v>-3.33957920902491</v>
       </c>
       <c r="D93">
-        <v>6.72228522002522</v>
+        <v>6.68770079097509</v>
       </c>
       <c r="E93">
-        <v>12.58744</v>
+        <v>12.73328</v>
       </c>
       <c r="F93">
-        <v>13.27144</v>
+        <v>13.41728</v>
       </c>
       <c r="G93">
         <v>3.39</v>
@@ -8907,37 +8907,37 @@
         <v>1.29</v>
       </c>
       <c r="M93">
-        <v>3.129405552</v>
+        <v>3.163794624</v>
       </c>
       <c r="N93">
-        <v>-1.839405552</v>
+        <v>-1.873794624</v>
       </c>
       <c r="O93">
-        <v>-0.4414573324800001</v>
+        <v>-0.44971070976</v>
       </c>
       <c r="P93">
-        <v>-1.39794821952</v>
+        <v>-1.42408391424</v>
       </c>
       <c r="Q93">
-        <v>0.4020517804799997</v>
+        <v>0.3759160857599999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5979581484093985</v>
+        <v>0.6669779169605735</v>
       </c>
       <c r="T93">
-        <v>7.60066474793373</v>
+        <v>8.550747841425448</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.09893252723416908</v>
+        <v>0.09785717367727595</v>
       </c>
       <c r="W93">
-        <v>0.2124717100781829</v>
+        <v>0.2127252784468983</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4122188634757046</v>
+        <v>0.4077382236553164</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2490654895279923</v>
+        <v>0.2509654895279924</v>
       </c>
       <c r="C94">
-        <v>-3.33957920902491</v>
+        <v>-3.519649603501387</v>
       </c>
       <c r="D94">
-        <v>6.68770079097509</v>
+        <v>6.653470396498613</v>
       </c>
       <c r="E94">
-        <v>12.73328</v>
+        <v>12.87912</v>
       </c>
       <c r="F94">
-        <v>13.41728</v>
+        <v>13.56312</v>
       </c>
       <c r="G94">
         <v>3.39</v>
@@ -8989,37 +8989,37 @@
         <v>1.29</v>
       </c>
       <c r="M94">
-        <v>3.163794624</v>
+        <v>3.198183696</v>
       </c>
       <c r="N94">
-        <v>-1.873794624</v>
+        <v>-1.908183696</v>
       </c>
       <c r="O94">
-        <v>-0.44971070976</v>
+        <v>-0.45796408704</v>
       </c>
       <c r="P94">
-        <v>-1.42408391424</v>
+        <v>-1.45021960896</v>
       </c>
       <c r="Q94">
-        <v>0.3759160857599999</v>
+        <v>0.3497803910399997</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.6669779169605735</v>
+        <v>0.7557176193835128</v>
       </c>
       <c r="T94">
-        <v>8.550747841425448</v>
+        <v>9.772283247343372</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.09785717367727595</v>
+        <v>0.09680494600332673</v>
       </c>
       <c r="W94">
-        <v>0.2127252784468983</v>
+        <v>0.2129733937324156</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.4077382236553164</v>
+        <v>0.4033539416805281</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2509654895279924</v>
+        <v>0.2528654895279923</v>
       </c>
       <c r="C95">
-        <v>-3.519649603501387</v>
+        <v>-3.699371372003068</v>
       </c>
       <c r="D95">
-        <v>6.653470396498613</v>
+        <v>6.619588627996933</v>
       </c>
       <c r="E95">
-        <v>12.87912</v>
+        <v>13.02496</v>
       </c>
       <c r="F95">
-        <v>13.56312</v>
+        <v>13.70896</v>
       </c>
       <c r="G95">
         <v>3.39</v>
@@ -9071,37 +9071,37 @@
         <v>1.29</v>
       </c>
       <c r="M95">
-        <v>3.198183696</v>
+        <v>3.232572768</v>
       </c>
       <c r="N95">
-        <v>-1.908183696</v>
+        <v>-1.942572768</v>
       </c>
       <c r="O95">
-        <v>-0.45796408704</v>
+        <v>-0.4662174643200001</v>
       </c>
       <c r="P95">
-        <v>-1.45021960896</v>
+        <v>-1.47635530368</v>
       </c>
       <c r="Q95">
-        <v>0.3497803910399997</v>
+        <v>0.3236446963199997</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.7557176193835128</v>
+        <v>0.8740372226140983</v>
       </c>
       <c r="T95">
-        <v>9.772283247343372</v>
+        <v>11.4009971219006</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.09680494600332673</v>
+        <v>0.09577510615222751</v>
       </c>
       <c r="W95">
-        <v>0.2129733937324156</v>
+        <v>0.2132162299693048</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.4033539416805281</v>
+        <v>0.399062942300948</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2528654895279923</v>
+        <v>0.2547654895279924</v>
       </c>
       <c r="C96">
-        <v>-3.699371372003068</v>
+        <v>-3.878749813517183</v>
       </c>
       <c r="D96">
-        <v>6.619588627996933</v>
+        <v>6.586050186482817</v>
       </c>
       <c r="E96">
-        <v>13.02496</v>
+        <v>13.1708</v>
       </c>
       <c r="F96">
-        <v>13.70896</v>
+        <v>13.8548</v>
       </c>
       <c r="G96">
         <v>3.39</v>
@@ -9153,37 +9153,37 @@
         <v>1.29</v>
       </c>
       <c r="M96">
-        <v>3.232572768</v>
+        <v>3.26696184</v>
       </c>
       <c r="N96">
-        <v>-1.942572768</v>
+        <v>-1.976961840000001</v>
       </c>
       <c r="O96">
-        <v>-0.4662174643200001</v>
+        <v>-0.4744708416000001</v>
       </c>
       <c r="P96">
-        <v>-1.47635530368</v>
+        <v>-1.502490998400001</v>
       </c>
       <c r="Q96">
-        <v>0.3236446963199997</v>
+        <v>0.2975090015999995</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8740372226140983</v>
+        <v>1.039684667136919</v>
       </c>
       <c r="T96">
-        <v>11.4009971219006</v>
+        <v>13.68119654628073</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.09577510615222751</v>
+        <v>0.0947669471400988</v>
       </c>
       <c r="W96">
-        <v>0.2132162299693048</v>
+        <v>0.2134539538643647</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.399062942300948</v>
+        <v>0.3948622797504117</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2547654895279924</v>
+        <v>0.2566654895279924</v>
       </c>
       <c r="C97">
-        <v>-3.878749813517183</v>
+        <v>-4.057790120182094</v>
       </c>
       <c r="D97">
-        <v>6.586050186482817</v>
+        <v>6.552849879817907</v>
       </c>
       <c r="E97">
-        <v>13.1708</v>
+        <v>13.31664</v>
       </c>
       <c r="F97">
-        <v>13.8548</v>
+        <v>14.00064</v>
       </c>
       <c r="G97">
         <v>3.39</v>
@@ -9235,37 +9235,37 @@
         <v>1.29</v>
       </c>
       <c r="M97">
-        <v>3.26696184</v>
+        <v>3.301350912</v>
       </c>
       <c r="N97">
-        <v>-1.976961840000001</v>
+        <v>-2.011350912</v>
       </c>
       <c r="O97">
-        <v>-0.4744708416000001</v>
+        <v>-0.48272421888</v>
       </c>
       <c r="P97">
-        <v>-1.502490998400001</v>
+        <v>-1.52862669312</v>
       </c>
       <c r="Q97">
-        <v>0.2975090015999995</v>
+        <v>0.2713733068799999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.039684667136919</v>
+        <v>1.288155833921149</v>
       </c>
       <c r="T97">
-        <v>13.68119654628073</v>
+        <v>17.10149568285092</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.0947669471400988</v>
+        <v>0.09377979144072277</v>
       </c>
       <c r="W97">
-        <v>0.2134539538643647</v>
+        <v>0.2136867251782776</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3948622797504117</v>
+        <v>0.3907491310030117</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2566654895279923</v>
+        <v>0.2585654895279924</v>
       </c>
       <c r="C98">
-        <v>-4.057790120182089</v>
+        <v>-4.236497379966908</v>
       </c>
       <c r="D98">
-        <v>6.552849879817909</v>
+        <v>6.51998262003309</v>
       </c>
       <c r="E98">
-        <v>13.31664</v>
+        <v>13.46248</v>
       </c>
       <c r="F98">
-        <v>14.00064</v>
+        <v>14.14648</v>
       </c>
       <c r="G98">
         <v>3.39</v>
@@ -9317,37 +9317,37 @@
         <v>1.29</v>
       </c>
       <c r="M98">
-        <v>3.301350912</v>
+        <v>3.335739984</v>
       </c>
       <c r="N98">
-        <v>-2.011350912</v>
+        <v>-2.045739984</v>
       </c>
       <c r="O98">
-        <v>-0.48272421888</v>
+        <v>-0.49097759616</v>
       </c>
       <c r="P98">
-        <v>-1.52862669312</v>
+        <v>-1.55476238784</v>
       </c>
       <c r="Q98">
-        <v>0.2713733068799999</v>
+        <v>0.2452376121600002</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.288155833921146</v>
+        <v>1.702274445228194</v>
       </c>
       <c r="T98">
-        <v>17.10149568285087</v>
+        <v>22.80199424380117</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.09377979144072278</v>
+        <v>0.09281298946710709</v>
       </c>
       <c r="W98">
-        <v>0.2136867251782776</v>
+        <v>0.2139146970836562</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3907491310030116</v>
+        <v>0.3867207894462796</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2585654895279924</v>
+        <v>0.2604654895279923</v>
       </c>
       <c r="C99">
-        <v>-4.236497379966908</v>
+        <v>-4.414876579270883</v>
       </c>
       <c r="D99">
-        <v>6.51998262003309</v>
+        <v>6.487443420729117</v>
       </c>
       <c r="E99">
-        <v>13.46248</v>
+        <v>13.60832</v>
       </c>
       <c r="F99">
-        <v>14.14648</v>
+        <v>14.29232</v>
       </c>
       <c r="G99">
         <v>3.39</v>
@@ -9399,37 +9399,37 @@
         <v>1.29</v>
       </c>
       <c r="M99">
-        <v>3.335739984</v>
+        <v>3.370129056</v>
       </c>
       <c r="N99">
-        <v>-2.045739984</v>
+        <v>-2.080129056000001</v>
       </c>
       <c r="O99">
-        <v>-0.49097759616</v>
+        <v>-0.4992309734400001</v>
       </c>
       <c r="P99">
-        <v>-1.55476238784</v>
+        <v>-1.580898082560001</v>
       </c>
       <c r="Q99">
-        <v>0.2452376121600002</v>
+        <v>0.2191019174399995</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.702274445228194</v>
+        <v>2.530511667842291</v>
       </c>
       <c r="T99">
-        <v>22.80199424380117</v>
+        <v>34.20299136570174</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.09281298946710709</v>
+        <v>0.09186591814601415</v>
       </c>
       <c r="W99">
-        <v>0.2139146970836562</v>
+        <v>0.2141380165011699</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.3867207894462796</v>
+        <v>0.3827746589417256</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2604654895279923</v>
+        <v>0.2623654895279923</v>
       </c>
       <c r="C100">
-        <v>-4.414876579270883</v>
+        <v>-4.592932605445323</v>
       </c>
       <c r="D100">
-        <v>6.487443420729117</v>
+        <v>6.455227394554676</v>
       </c>
       <c r="E100">
-        <v>13.60832</v>
+        <v>13.75416</v>
       </c>
       <c r="F100">
-        <v>14.29232</v>
+        <v>14.43816</v>
       </c>
       <c r="G100">
         <v>3.39</v>
@@ -9481,37 +9481,37 @@
         <v>1.29</v>
       </c>
       <c r="M100">
-        <v>3.370129056</v>
+        <v>3.404518128</v>
       </c>
       <c r="N100">
-        <v>-2.080129056000001</v>
+        <v>-2.114518128</v>
       </c>
       <c r="O100">
-        <v>-0.4992309734400001</v>
+        <v>-0.5074843507200001</v>
       </c>
       <c r="P100">
-        <v>-1.580898082560001</v>
+        <v>-1.60703377728</v>
       </c>
       <c r="Q100">
-        <v>0.2191019174399995</v>
+        <v>0.1929662227199997</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.530511667842291</v>
+        <v>5.015223335684581</v>
       </c>
       <c r="T100">
-        <v>34.20299136570174</v>
+        <v>68.40598273140348</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.09186591814601415</v>
+        <v>0.09093797957888268</v>
       </c>
       <c r="W100">
-        <v>0.2141380165011699</v>
+        <v>0.2143568244152995</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3827746589417256</v>
+        <v>0.3789082482453446</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2623654895279923</v>
-      </c>
-      <c r="C101">
-        <v>-4.592932605445323</v>
-      </c>
-      <c r="D101">
-        <v>6.455227394554676</v>
-      </c>
-      <c r="E101">
-        <v>13.75416</v>
-      </c>
-      <c r="F101">
-        <v>14.43816</v>
-      </c>
-      <c r="G101">
-        <v>3.39</v>
-      </c>
-      <c r="H101">
-        <v>13.9</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>3.09</v>
-      </c>
-      <c r="K101">
-        <v>1.8</v>
-      </c>
-      <c r="L101">
-        <v>1.29</v>
-      </c>
-      <c r="M101">
-        <v>3.404518128</v>
-      </c>
-      <c r="N101">
-        <v>-2.114518128</v>
-      </c>
-      <c r="O101">
-        <v>-0.5074843507200001</v>
-      </c>
-      <c r="P101">
-        <v>-1.60703377728</v>
-      </c>
-      <c r="Q101">
-        <v>0.1929662227199997</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.015223335684581</v>
-      </c>
-      <c r="T101">
-        <v>68.40598273140348</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.09093797957888268</v>
-      </c>
-      <c r="W101">
-        <v>0.2143568244152995</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.3789082482453446</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
